--- a/冒险者基础规则.xlsx
+++ b/冒险者基础规则.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="基本规则" sheetId="6" r:id="rId1"/>
@@ -51,91 +51,91 @@
     <t>1.写在最开始的话</t>
   </si>
   <si>
-    <t>2.这不是D&amp;D</t>
-  </si>
-  <si>
-    <t>3.PVE？还是PVP？</t>
+    <t>2.别用旧习惯跑新规则</t>
+  </si>
+  <si>
+    <t>3.尽信书不如无书</t>
   </si>
   <si>
     <t>在了解斯诺德跑团的具体规则之前，请先阅读并认同以下共识，这些内容对您和主持人（DM）之间的良好合作至关重要。斯诺德世界拥有大量文本，如果您没有耐心读完并记住本部分的核心原则，那么您一定不适合参与本游戏。提前明确这一点，有助于双方避免不必要的时间浪费</t>
   </si>
   <si>
-    <t>斯诺德跑团在创作中借鉴了D&amp;D、COC、迷雾之城等TRPG规则，同时也包含大量原创机制。请不要直接套用您在其他游戏中的经验，因为斯诺德的规则有意做了不同甚至相反的调整,如果不主动了解斯诺德自身的规则，而只是生硬地移植其他游戏的玩法，您将必然在推进游戏的过程中陷入困境</t>
+    <t>斯诺德跑团在创作中借鉴了D&amp;D、COC、最终物语、迷雾之城等TRPG规则，同时也包含大量原创机制。它不是这些规则的简单拼接或换名版本，请不要直接套用您在其他游戏中的经验、判定和操作习惯，因为斯诺德的规则有意做了不同、甚至相反的调整,若不先了解斯诺德自身规则，而是生硬地移植其他游戏的玩法，您将必然在推进游戏的过程中陷入困境，请先读规则，或向主持人确认，再决定如何行动。</t>
+  </si>
+  <si>
+    <t>规则书是游戏的骨架和参考，但它不可能穷尽所有情境、组合与临场变化，文本总有边界，字面争辩无法替代对当前场景的判断。请不要在规则书里钻牛角尖；当出现规则未覆盖、表述模糊或与现场冲突的情况时，以主持人的最终判定为准。若有疑问，可以在合适时机提出，但不要因抠字眼打断游戏节奏</t>
+  </si>
+  <si>
+    <t>4.PVE？还是PVP？</t>
+  </si>
+  <si>
+    <t>5.我是尼古拉斯·赵·云殇~</t>
+  </si>
+  <si>
+    <t>6.这是最坏的时代</t>
   </si>
   <si>
     <t>主持人在游戏过程中的存在，是为了帮助玩家角色顺利推进当前的故事，请多与主持人交流和互动，而不是把主持人想象成对立面。这种对抗行为没有任何意义，因为在这个世界观下，主持人实际上拥有无限的资源可供使用。请记住：这不是一个对抗性质的游戏</t>
   </si>
   <si>
-    <t>4.了解这里的风土人情</t>
-  </si>
-  <si>
-    <t>5.我是尼古拉斯·赵·云殇~</t>
-  </si>
-  <si>
-    <t>6.说，你要干嘛</t>
-  </si>
-  <si>
-    <t>完整了解整个斯诺德世界的背景故事并非必须事项，但至少知晓一些基本的人际关系或相关内容，会更有利于您顺利游玩，遇到不了解的地方，可以询问主持人，或通过检定去了解。请不要在受挫时用“我并不了解”来搪塞自己的失误</t>
-  </si>
-  <si>
     <t>传奇后裔、天命之人、权勋世家...为自己设计一个过于炫酷的背景故事并不现实，您当前只是一名1级冒险者，角色创建时设定的庞大人脉与显赫身世在实际游戏中并不会生效，创作过多额外内容只会带来落差感。您的故事才刚刚开始，而不是早已在背景中完美落幕</t>
   </si>
   <si>
-    <t>或者说，告诉DM你要干嘛。如果您自己都不清楚行动的目标，那么这可能并不是一个合适的选择，只有在了解您角色行为逻辑的前提下，主持人才能够更准确地给出符合您期望的回应</t>
-  </si>
-  <si>
-    <t>7.万事皆有代价</t>
-  </si>
-  <si>
-    <t>8.别把简单问题复杂化</t>
-  </si>
-  <si>
-    <t>9.假如...？</t>
+    <t>斯诺德的价值观与道德水准大致处于中世纪水平，贵族与阶级制度是常态，执法队伍服务的对象往往是王室或官方机构，而非玩家角色或平民。大多数人受限于时代背景，并不会主动争取更多权益，请不要用现实中的国内标准去衡量，若需类比，他们的思维方式更接近海外某些地区的行事风格</t>
+  </si>
+  <si>
+    <t>7.这是最好的时代</t>
+  </si>
+  <si>
+    <t>8.世界总是照常运转</t>
+  </si>
+  <si>
+    <t>9.万事皆有代价</t>
+  </si>
+  <si>
+    <t>这并非一个由死亡与悲剧构成的故事。作为冒险者，玩家角色拥有无限的可能性，成长本身就是你们最大的优势，只要坚持不懈当前的困境和难题并非无法消除。对心存希望的人而言，只要不放弃就始终存在翻盘的机会</t>
+  </si>
+  <si>
+    <t>你们不总是这个世界的主角，但也绝非寂寂无名的凡夫，每个人都会拥有闪光点和获得聚光灯的时刻。但请记住：当你们停滞不前时，故事中的敌人或事物并不会停下脚步等待，斯诺德世界的时间线将按既定进程推进，游戏的难度与当前等级无关，而是与游玩的时长和你们的抉择相关</t>
   </si>
   <si>
     <t>在采取某一行动之前，请先想清楚需要付出的代价，对于玩家角色所在的王国或其他历史悠久的秩序势力而言，他们拥有丰富的经验来应对不守规矩的冒险者。作恶可能带来巨大收益，但面对秩序势力的打击时，请务必做好心理准备</t>
   </si>
   <si>
+    <t>10.关于社交</t>
+  </si>
+  <si>
+    <t>11.不懂就问，先查再动</t>
+  </si>
+  <si>
+    <t>12.说，您要干嘛</t>
+  </si>
+  <si>
+    <t>斯诺德世界中的人物行为逻辑较为贴近现实，把非玩家角色（NPC）当作活生生的人来看待，会更有利于游戏顺利进行。请记住，每一位人物都有不同的行事准则和处事方式：农民、商人、士兵或贵族的立场各不相同，对所有人使用同一套说辞，绝不会是合适的选择</t>
+  </si>
+  <si>
+    <t>您不必完整了解整个斯诺德世界的背景故事，但至少知晓一些基本的人际关系、势力、常识或当前剧情相关的内容，会更有利于您顺利游玩，遇到不了解的地方，可以询问主持人，或通过检定去了解。请不要在受挫时用“我并不了解”来搪塞自己的失误；比起在陌生领域直接操作，先问、先查、先确认，通常是更稳妥的选择</t>
+  </si>
+  <si>
+    <t>告诉主持人您要做什么，也告诉主持人您的具体假设。与其只说“我要用某能力”、或空泛地问“假如我这样用行不行”，不如说清：角色想达成什么、打算怎么做、处于什么场景、依赖哪些条件。主持人只有理解您角色的行为逻辑和具体情境，才能判断是否可行、是否需要检定，并给出符合您期望的回应。若意图模糊，主持人只能按字面推断，结果可能与您期望不同；若确实需要提前确认，请描述详细的假设场景与目的</t>
+  </si>
+  <si>
+    <t>13.没有理所当然的成功</t>
+  </si>
+  <si>
+    <t>14.别把简单问题复杂化</t>
+  </si>
+  <si>
+    <t>15.主动求助，才有转机</t>
+  </si>
+  <si>
+    <t>您的角色可能在某些能力上天赋异禀，也可能在另一些方面逊于常人，每个人都有擅长与不擅长的事情。当您要执行某个操作时，如果角色没有对应熟练度、知识或经验，他不会因为“我应该会”“我的理解是”“我以为是”就自动成功或获得收益。同样，玩家本人知道，不等于角色知道；玩家本人会，也不等于角色会；请把玩家知识与角色能力分开，以角色卡、背景和当前情境为准</t>
+  </si>
+  <si>
     <t>斯诺德跑团中不会出现必须依靠现实中的特定专业知识才能破解的谜题，冒险故事的逻辑通常不会太复杂，如果团队迟迟无法获得线索、剧情陷入僵局，或者主持人给出了明确的否定答复，又或者检定掷出较高数值后依然一无所获，这很可能是在提醒你们：不要再进行无意义的行为了</t>
   </si>
   <si>
-    <t>在游戏之外询问主持人“假如我这样使用能力是否可行”是没有意义的，斯诺德跑团中的一切行为都需要结合当前场景的实际状况来判断，即使主持人在游戏外多次给予肯定答复，实际游戏中也可能会得出完全相反的结果</t>
-  </si>
-  <si>
-    <t>10.没有什么是理所当然的</t>
-  </si>
-  <si>
-    <t>11.关于社交</t>
-  </si>
-  <si>
-    <t>12.摆烂不救</t>
-  </si>
-  <si>
-    <t>您的角色在某些能力上可能天赋异禀，但也可能在另一些方面逊于常人，每个人都有擅长与不擅长的事情，当需要执行某个操作时，如果您没有对应的熟练度或并不精通，那么您的角色并不会因为“我应该会”“我的理解是”“我以为是”等说辞而自动完成该事项</t>
-  </si>
-  <si>
-    <t>斯诺德世界中的人物行为逻辑较为贴近现实，把非玩家角色（NPC）当作活生生的人来看待，会更有利于游戏顺利进行。请记住，每一位人物都有不同的行事准则和处事方式：农民、商人、士兵或贵族的立场各不相同，对所有人使用同一套说辞，绝不会是合适的选择</t>
-  </si>
-  <si>
-    <t>主持人不会为消极游玩的玩家投入资源，如果因为一时受挫而故意摆烂、放弃配合，这样的玩家通常会在后续被优化出游戏。请保持积极的参与态度，即使遇到困难也要尝试寻找解决方式或与主持人进行沟通</t>
-  </si>
-  <si>
-    <t>13.这是最坏的时代</t>
-  </si>
-  <si>
-    <t>14.这是最好的时代</t>
-  </si>
-  <si>
-    <t>15.世界总是照常运转</t>
-  </si>
-  <si>
-    <t>斯诺德的价值观与道德水准大致处于中世纪水平，贵族与阶级制度是常态，执法队伍服务的对象往往是王室或官方机构，而非玩家角色或平民。大多数人受限于时代背景，并不会主动争取更多权益，请不要用现实中的国内标准去衡量，若需类比，他们的思维方式更接近海外某些地区的行事风格</t>
-  </si>
-  <si>
-    <t>这并非一个由死亡与悲剧构成的故事。作为冒险者，玩家角色拥有无限的可能性，成长本身就是你们最大的优势，只要坚持不懈当前的困境和难题并非无法消除。对心存希望的人而言，只要不放弃就始终存在翻盘的机会</t>
-  </si>
-  <si>
-    <t>你们不总是这个世界的主角，但也绝非寂寂无名的凡夫，每个人都会拥有闪光点和获得聚光灯的时刻。但请记住：当你们停滞不前时，故事中的敌人或事物并不会停下脚步等待，斯诺德世界的时间线将按既定进程推进，游戏的难度与当前等级无关，而是与游玩的时长和你们的抉择相关</t>
+    <t>主持人不会把资源持续投入给消极游玩的玩家，若您因一时受挫就故意摆烂、拒绝配合，通常只会让局面更糟，并可能在后续被优化出游戏。请保持积极的参与态度；遇到困难时，先尝试寻找解决方式，或主动与主持人沟通。只有您先表现出“我想继续玩、我想解决问题”，主持人才有办法真正帮到您</t>
   </si>
   <si>
     <t>基础熟练项的检定规则</t>
@@ -3987,7 +3987,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4237,12 +4237,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4255,18 +4249,6 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4279,18 +4261,9 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4303,15 +4276,6 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="58" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4333,30 +4297,6 @@
     <xf numFmtId="0" fontId="1" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4399,24 +4339,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4432,9 +4357,6 @@
     <xf numFmtId="0" fontId="1" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4474,57 +4396,6 @@
     <xf numFmtId="0" fontId="1" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4635,6 +4506,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4961,7 +4841,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:R37"/>
+  <dimension ref="B2:R42"/>
   <sheetFormatPr defaultColWidth="10.6333333333333" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="10.6333333333333" style="22" customWidth="1"/>
@@ -4973,7 +4853,7 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="215"/>
+      <c r="E2" s="172"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -5086,84 +4966,84 @@
       <c r="R8" s="10"/>
     </row>
     <row r="9" customHeight="1" spans="2:18">
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="13"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="13"/>
-    </row>
-    <row r="11" customHeight="1" spans="2:18">
-      <c r="B11" s="2" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="10"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="10"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" customHeight="1" spans="2:18">
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="13"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="13"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="13"/>
+    </row>
+    <row r="12" customHeight="1" spans="2:18">
+      <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
-      <c r="H11" s="2" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="4"/>
+      <c r="H12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="4"/>
-      <c r="N11" s="2" t="s">
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="4"/>
+      <c r="N12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="4"/>
-    </row>
-    <row r="12" customHeight="1" spans="2:18">
-      <c r="B12" s="5" t="s">
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="4"/>
+    </row>
+    <row r="13" customHeight="1" spans="2:18">
+      <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="7"/>
-      <c r="H12" s="5" t="s">
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="H13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="7"/>
-      <c r="N12" s="5" t="s">
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="7"/>
+      <c r="N13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="7"/>
-    </row>
-    <row r="13" customHeight="1" spans="2:18">
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="10"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="10"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="7"/>
     </row>
     <row r="14" customHeight="1" spans="2:18">
       <c r="B14" s="8"/>
@@ -5200,101 +5080,101 @@
       <c r="R15" s="10"/>
     </row>
     <row r="16" customHeight="1" spans="2:18">
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="13"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="13"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="13"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="10"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="10"/>
+    </row>
+    <row r="17" customHeight="1" spans="2:18">
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="10"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="10"/>
     </row>
     <row r="18" customHeight="1" spans="2:18">
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="13"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="13"/>
+    </row>
+    <row r="20" customHeight="1" spans="2:18">
+      <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="4"/>
-      <c r="H18" s="2" t="s">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4"/>
+      <c r="H20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="4"/>
-      <c r="N18" s="2" t="s">
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="4"/>
+      <c r="N20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="4"/>
-    </row>
-    <row r="19" customHeight="1" spans="2:18">
-      <c r="B19" s="5" t="s">
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="4"/>
+    </row>
+    <row r="21" customHeight="1" spans="2:18">
+      <c r="B21" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="7"/>
-      <c r="H19" s="5" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
+      <c r="H21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="7"/>
-      <c r="N19" s="5" t="s">
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="7"/>
+      <c r="N21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="7"/>
-    </row>
-    <row r="20" customHeight="1" spans="2:18">
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="10"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="10"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="10"/>
-    </row>
-    <row r="21" customHeight="1" spans="2:18">
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="10"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="10"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="10"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="7"/>
     </row>
     <row r="22" customHeight="1" spans="2:18">
       <c r="B22" s="8"/>
@@ -5314,249 +5194,334 @@
       <c r="R22" s="10"/>
     </row>
     <row r="23" customHeight="1" spans="2:18">
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="13"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="13"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="13"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="10"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="10"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="10"/>
+    </row>
+    <row r="24" customHeight="1" spans="2:18">
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="10"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="10"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="10"/>
     </row>
     <row r="25" customHeight="1" spans="2:18">
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="10"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="10"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="10"/>
+    </row>
+    <row r="26" customHeight="1" spans="2:18">
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="13"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="13"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="13"/>
+    </row>
+    <row r="28" customHeight="1" spans="2:18">
+      <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="4"/>
-      <c r="H25" s="2" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="4"/>
+      <c r="H28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="4"/>
-      <c r="N25" s="2" t="s">
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="4"/>
+      <c r="N28" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="4"/>
-    </row>
-    <row r="26" customHeight="1" spans="2:18">
-      <c r="B26" s="5" t="s">
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="4"/>
+    </row>
+    <row r="29" customHeight="1" spans="2:18">
+      <c r="B29" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="7"/>
-      <c r="H26" s="5" t="s">
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7"/>
+      <c r="H29" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="7"/>
-      <c r="N26" s="5" t="s">
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="7"/>
+      <c r="N29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="7"/>
-    </row>
-    <row r="27" customHeight="1" spans="2:18">
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="10"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="10"/>
-    </row>
-    <row r="28" customHeight="1" spans="2:18">
-      <c r="B28" s="8"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="10"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="10"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="10"/>
-    </row>
-    <row r="29" customHeight="1" spans="2:18">
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="10"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="10"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="10"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="2:18">
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="13"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="13"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="13"/>
+      <c r="B30" s="173"/>
+      <c r="C30" s="174"/>
+      <c r="D30" s="174"/>
+      <c r="E30" s="174"/>
+      <c r="F30" s="175"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="10"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="10"/>
+    </row>
+    <row r="31" customHeight="1" spans="2:18">
+      <c r="B31" s="8"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="10"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="10"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="10"/>
     </row>
     <row r="32" customHeight="1" spans="2:18">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="8"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="10"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="10"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="10"/>
+    </row>
+    <row r="33" customHeight="1" spans="2:18">
+      <c r="B33" s="8"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="10"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="10"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="10"/>
+    </row>
+    <row r="34" customHeight="1" spans="2:18">
+      <c r="B34" s="11"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="13"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="13"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="12"/>
+      <c r="Q34" s="12"/>
+      <c r="R34" s="13"/>
+    </row>
+    <row r="36" customHeight="1" spans="2:18">
+      <c r="B36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="4"/>
-      <c r="H32" s="2" t="s">
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="4"/>
+      <c r="H36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="4"/>
-      <c r="N32" s="2" t="s">
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="4"/>
+      <c r="N36" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="4"/>
-    </row>
-    <row r="33" customHeight="1" spans="2:18">
-      <c r="B33" s="5" t="s">
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="4"/>
+    </row>
+    <row r="37" customHeight="1" spans="2:18">
+      <c r="B37" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="7"/>
-      <c r="H33" s="5" t="s">
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="7"/>
+      <c r="H37" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="7"/>
-      <c r="N33" s="5" t="s">
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="7"/>
+      <c r="N37" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="7"/>
-    </row>
-    <row r="34" customHeight="1" spans="2:18">
-      <c r="B34" s="8"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="10"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="10"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="10"/>
-    </row>
-    <row r="35" customHeight="1" spans="2:18">
-      <c r="B35" s="8"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="10"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="10"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="10"/>
-    </row>
-    <row r="36" customHeight="1" spans="2:18">
-      <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="10"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="10"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="10"/>
-    </row>
-    <row r="37" customHeight="1" spans="2:18">
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="13"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="13"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="12"/>
-      <c r="P37" s="12"/>
-      <c r="Q37" s="12"/>
-      <c r="R37" s="13"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="7"/>
+    </row>
+    <row r="38" customHeight="1" spans="2:18">
+      <c r="B38" s="173"/>
+      <c r="C38" s="174"/>
+      <c r="D38" s="174"/>
+      <c r="E38" s="174"/>
+      <c r="F38" s="175"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="10"/>
+      <c r="N38" s="173"/>
+      <c r="O38" s="174"/>
+      <c r="P38" s="174"/>
+      <c r="Q38" s="174"/>
+      <c r="R38" s="175"/>
+    </row>
+    <row r="39" customHeight="1" spans="2:18">
+      <c r="B39" s="8"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="10"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="10"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="10"/>
+    </row>
+    <row r="40" customHeight="1" spans="2:18">
+      <c r="B40" s="8"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="10"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="10"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="10"/>
+    </row>
+    <row r="41" customHeight="1" spans="2:18">
+      <c r="B41" s="8"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="10"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="10"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="10"/>
+    </row>
+    <row r="42" customHeight="1" spans="2:18">
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="13"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="13"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="12"/>
+      <c r="P42" s="12"/>
+      <c r="Q42" s="12"/>
+      <c r="R42" s="13"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
@@ -5565,33 +5530,33 @@
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
     <mergeCell ref="N4:R4"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="H11:L11"/>
-    <mergeCell ref="N11:R11"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="N18:R18"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="H25:L25"/>
-    <mergeCell ref="N25:R25"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="H32:L32"/>
-    <mergeCell ref="N32:R32"/>
-    <mergeCell ref="B5:F9"/>
-    <mergeCell ref="H12:L16"/>
-    <mergeCell ref="N12:R16"/>
-    <mergeCell ref="B12:F16"/>
-    <mergeCell ref="H5:L9"/>
-    <mergeCell ref="N5:R9"/>
-    <mergeCell ref="B19:F23"/>
-    <mergeCell ref="H19:L23"/>
-    <mergeCell ref="N19:R23"/>
-    <mergeCell ref="B26:F30"/>
-    <mergeCell ref="H26:L30"/>
-    <mergeCell ref="N26:R30"/>
-    <mergeCell ref="B33:F37"/>
-    <mergeCell ref="H33:L37"/>
-    <mergeCell ref="N33:R37"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="N12:R12"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="N20:R20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="H28:L28"/>
+    <mergeCell ref="N28:R28"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="H36:L36"/>
+    <mergeCell ref="N36:R36"/>
+    <mergeCell ref="B5:F10"/>
+    <mergeCell ref="H5:L10"/>
+    <mergeCell ref="N5:R10"/>
+    <mergeCell ref="H13:L18"/>
+    <mergeCell ref="N13:R18"/>
+    <mergeCell ref="B13:F18"/>
+    <mergeCell ref="B21:F26"/>
+    <mergeCell ref="H21:L26"/>
+    <mergeCell ref="N21:R26"/>
+    <mergeCell ref="B29:F34"/>
+    <mergeCell ref="H29:L34"/>
+    <mergeCell ref="N29:R34"/>
+    <mergeCell ref="B37:F42"/>
+    <mergeCell ref="H37:L42"/>
+    <mergeCell ref="N37:R42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -10148,13 +10113,13 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="4"/>
-      <c r="H4" s="137" t="s">
+      <c r="H4" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="177"/>
-      <c r="J4" s="177"/>
-      <c r="K4" s="177"/>
-      <c r="L4" s="138"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="77"/>
       <c r="N4" s="75" t="s">
         <v>36</v>
       </c>
@@ -10164,11 +10129,11 @@
       <c r="R4" s="77"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="10" customHeight="1" spans="2:18">
-      <c r="H5" s="140"/>
+      <c r="H5" s="78"/>
       <c r="I5" s="79"/>
       <c r="J5" s="79"/>
       <c r="K5" s="79"/>
-      <c r="L5" s="141"/>
+      <c r="L5" s="80"/>
       <c r="N5" s="78"/>
       <c r="O5" s="79"/>
       <c r="P5" s="79"/>
@@ -10179,15 +10144,15 @@
       <c r="B6" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="137" t="s">
+      <c r="D6" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="177"/>
-      <c r="F6" s="138"/>
-      <c r="H6" s="142"/>
-      <c r="I6" s="178"/>
-      <c r="J6" s="178"/>
-      <c r="K6" s="178"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="77"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
       <c r="L6" s="72"/>
       <c r="N6" s="78"/>
       <c r="O6" s="79"/>
@@ -10197,9 +10162,9 @@
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="2:18">
       <c r="B7" s="32"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="179"/>
-      <c r="F7" s="141"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="80"/>
       <c r="N7" s="78"/>
       <c r="O7" s="79"/>
       <c r="P7" s="79"/>
@@ -10208,8 +10173,8 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="2:18">
       <c r="B8" s="29"/>
-      <c r="D8" s="142"/>
-      <c r="E8" s="178"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="82"/>
       <c r="F8" s="72"/>
       <c r="H8" s="2" t="s">
         <v>39</v>
@@ -10235,11 +10200,11 @@
       <c r="B10" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="137" t="s">
+      <c r="D10" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="177"/>
-      <c r="F10" s="138"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="77"/>
       <c r="H10" s="2" t="s">
         <v>42</v>
       </c>
@@ -10254,10 +10219,10 @@
       <c r="R10" s="80"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="2:18">
-      <c r="B11" s="180"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="179"/>
-      <c r="F11" s="141"/>
+      <c r="B11" s="137"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="136"/>
+      <c r="F11" s="80"/>
       <c r="N11" s="78"/>
       <c r="O11" s="79"/>
       <c r="P11" s="79"/>
@@ -10265,237 +10230,237 @@
       <c r="R11" s="80"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="2:18">
-      <c r="B12" s="180"/>
-      <c r="D12" s="142"/>
-      <c r="E12" s="178"/>
+      <c r="B12" s="137"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="82"/>
       <c r="F12" s="72"/>
       <c r="H12" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="J12" s="137" t="s">
+      <c r="J12" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="K12" s="177"/>
-      <c r="L12" s="138"/>
+      <c r="K12" s="76"/>
+      <c r="L12" s="77"/>
       <c r="N12" s="81"/>
       <c r="O12" s="82"/>
       <c r="P12" s="82"/>
       <c r="Q12" s="82"/>
-      <c r="R12" s="83"/>
+      <c r="R12" s="72"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="10" customHeight="1" spans="2:18">
-      <c r="B13" s="180"/>
+      <c r="B13" s="137"/>
       <c r="H13" s="32"/>
-      <c r="J13" s="140"/>
-      <c r="K13" s="179"/>
-      <c r="L13" s="141"/>
+      <c r="J13" s="78"/>
+      <c r="K13" s="136"/>
+      <c r="L13" s="80"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="2:18">
-      <c r="B14" s="180"/>
-      <c r="D14" s="137" t="s">
+      <c r="B14" s="137"/>
+      <c r="D14" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="177"/>
-      <c r="F14" s="138"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="77"/>
       <c r="H14" s="29"/>
-      <c r="J14" s="140"/>
-      <c r="K14" s="179"/>
-      <c r="L14" s="141"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="80"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="2:18">
-      <c r="B15" s="180"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="179"/>
-      <c r="F15" s="141"/>
-      <c r="J15" s="140"/>
-      <c r="K15" s="179"/>
-      <c r="L15" s="141"/>
+      <c r="B15" s="137"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="80"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="136"/>
+      <c r="L15" s="80"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="2:18">
-      <c r="B16" s="180"/>
-      <c r="D16" s="140"/>
-      <c r="E16" s="179"/>
-      <c r="F16" s="141"/>
+      <c r="B16" s="137"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="80"/>
       <c r="H16" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="140"/>
-      <c r="K16" s="179"/>
-      <c r="L16" s="141"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="136"/>
+      <c r="L16" s="80"/>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B17" s="180"/>
-      <c r="D17" s="140"/>
-      <c r="E17" s="179"/>
-      <c r="F17" s="141"/>
+      <c r="B17" s="137"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="80"/>
       <c r="H17" s="32"/>
-      <c r="J17" s="140"/>
-      <c r="K17" s="179"/>
-      <c r="L17" s="141"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="80"/>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B18" s="180"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="178"/>
+      <c r="B18" s="137"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="82"/>
       <c r="F18" s="72"/>
       <c r="H18" s="29"/>
-      <c r="J18" s="140"/>
-      <c r="K18" s="179"/>
-      <c r="L18" s="141"/>
+      <c r="J18" s="78"/>
+      <c r="K18" s="136"/>
+      <c r="L18" s="80"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B19" s="180"/>
-      <c r="D19" s="181" t="s">
+      <c r="B19" s="137"/>
+      <c r="D19" s="138" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="137" t="s">
+      <c r="E19" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="138"/>
-      <c r="J19" s="140"/>
-      <c r="K19" s="179"/>
-      <c r="L19" s="141"/>
+      <c r="F19" s="77"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="136"/>
+      <c r="L19" s="80"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B20" s="180"/>
-      <c r="D20" s="182"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="141"/>
+      <c r="B20" s="137"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="80"/>
       <c r="H20" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="J20" s="140"/>
-      <c r="K20" s="179"/>
-      <c r="L20" s="141"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="80"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B21" s="180"/>
-      <c r="D21" s="183"/>
-      <c r="E21" s="142"/>
+      <c r="B21" s="137"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="81"/>
       <c r="F21" s="72"/>
       <c r="H21" s="32"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="179"/>
-      <c r="L21" s="141"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="136"/>
+      <c r="L21" s="80"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B22" s="180"/>
-      <c r="D22" s="184" t="s">
+      <c r="B22" s="137"/>
+      <c r="D22" s="141" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="137" t="s">
+      <c r="E22" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="138"/>
+      <c r="F22" s="77"/>
       <c r="H22" s="29"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="179"/>
-      <c r="L22" s="141"/>
+      <c r="J22" s="78"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="80"/>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B23" s="180"/>
-      <c r="D23" s="185"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="141"/>
-      <c r="J23" s="140"/>
-      <c r="K23" s="179"/>
-      <c r="L23" s="141"/>
+      <c r="B23" s="137"/>
+      <c r="D23" s="142"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="80"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="80"/>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B24" s="180"/>
-      <c r="D24" s="186"/>
-      <c r="E24" s="142"/>
+      <c r="B24" s="137"/>
+      <c r="D24" s="143"/>
+      <c r="E24" s="81"/>
       <c r="F24" s="72"/>
       <c r="H24" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="J24" s="140"/>
-      <c r="K24" s="179"/>
-      <c r="L24" s="141"/>
+      <c r="J24" s="78"/>
+      <c r="K24" s="136"/>
+      <c r="L24" s="80"/>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B25" s="180"/>
-      <c r="D25" s="187" t="s">
+      <c r="B25" s="137"/>
+      <c r="D25" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="137" t="s">
+      <c r="E25" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="138"/>
+      <c r="F25" s="77"/>
       <c r="H25" s="32"/>
-      <c r="J25" s="140"/>
-      <c r="K25" s="179"/>
-      <c r="L25" s="141"/>
+      <c r="J25" s="78"/>
+      <c r="K25" s="136"/>
+      <c r="L25" s="80"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B26" s="180"/>
-      <c r="D26" s="188"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="141"/>
+      <c r="B26" s="137"/>
+      <c r="D26" s="145"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="80"/>
       <c r="H26" s="29"/>
-      <c r="J26" s="142"/>
-      <c r="K26" s="178"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="82"/>
       <c r="L26" s="72"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B27" s="180"/>
-      <c r="D27" s="189"/>
-      <c r="E27" s="142"/>
+      <c r="B27" s="137"/>
+      <c r="D27" s="146"/>
+      <c r="E27" s="81"/>
       <c r="F27" s="72"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B28" s="180"/>
-      <c r="D28" s="190" t="s">
+      <c r="B28" s="137"/>
+      <c r="D28" s="147" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="137" t="s">
+      <c r="E28" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="138"/>
+      <c r="F28" s="77"/>
       <c r="H28" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="J28" s="137" t="s">
+      <c r="J28" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="K28" s="177"/>
-      <c r="L28" s="138"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="77"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B29" s="180"/>
-      <c r="D29" s="191"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="141"/>
+      <c r="B29" s="137"/>
+      <c r="D29" s="148"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="80"/>
       <c r="H29" s="32"/>
-      <c r="J29" s="140"/>
+      <c r="J29" s="78"/>
       <c r="K29" s="79"/>
-      <c r="L29" s="141"/>
+      <c r="L29" s="80"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B30" s="180"/>
-      <c r="D30" s="192"/>
-      <c r="E30" s="142"/>
+      <c r="B30" s="137"/>
+      <c r="D30" s="149"/>
+      <c r="E30" s="81"/>
       <c r="F30" s="72"/>
       <c r="H30" s="29"/>
-      <c r="J30" s="142"/>
-      <c r="K30" s="178"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="82"/>
       <c r="L30" s="72"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B31" s="180"/>
+      <c r="B31" s="137"/>
       <c r="D31" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="137" t="s">
+      <c r="E31" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="138"/>
+      <c r="F31" s="77"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B32" s="180"/>
+      <c r="B32" s="137"/>
       <c r="D32" s="32"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="141"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="80"/>
       <c r="H32" s="2" t="s">
         <v>57</v>
       </c>
@@ -10505,185 +10470,185 @@
       <c r="L32" s="4"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B33" s="180"/>
+      <c r="B33" s="137"/>
       <c r="D33" s="29"/>
-      <c r="E33" s="142"/>
+      <c r="E33" s="81"/>
       <c r="F33" s="72"/>
       <c r="H33" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="I33" s="129">
+      <c r="I33" s="109">
         <v>5</v>
       </c>
-      <c r="J33" s="130"/>
-      <c r="K33" s="129" t="s">
+      <c r="J33" s="110"/>
+      <c r="K33" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="L33" s="130"/>
+      <c r="L33" s="110"/>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B34" s="180"/>
-      <c r="D34" s="193" t="s">
+      <c r="B34" s="137"/>
+      <c r="D34" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="137" t="s">
+      <c r="E34" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="138"/>
-      <c r="H34" s="180"/>
-      <c r="I34" s="129">
+      <c r="F34" s="77"/>
+      <c r="H34" s="137"/>
+      <c r="I34" s="109">
         <v>10</v>
       </c>
-      <c r="J34" s="130"/>
-      <c r="K34" s="129" t="s">
+      <c r="J34" s="110"/>
+      <c r="K34" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="L34" s="130"/>
+      <c r="L34" s="110"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B35" s="180"/>
-      <c r="D35" s="194"/>
-      <c r="E35" s="140"/>
-      <c r="F35" s="141"/>
-      <c r="H35" s="180"/>
-      <c r="I35" s="129">
+      <c r="B35" s="137"/>
+      <c r="D35" s="151"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="80"/>
+      <c r="H35" s="137"/>
+      <c r="I35" s="109">
         <v>15</v>
       </c>
-      <c r="J35" s="130"/>
-      <c r="K35" s="129" t="s">
+      <c r="J35" s="110"/>
+      <c r="K35" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="L35" s="130"/>
+      <c r="L35" s="110"/>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B36" s="180"/>
-      <c r="D36" s="195"/>
-      <c r="E36" s="142"/>
+      <c r="B36" s="137"/>
+      <c r="D36" s="152"/>
+      <c r="E36" s="81"/>
       <c r="F36" s="72"/>
       <c r="H36" s="32"/>
-      <c r="I36" s="129">
+      <c r="I36" s="109">
         <v>20</v>
       </c>
-      <c r="J36" s="130"/>
-      <c r="K36" s="129" t="s">
+      <c r="J36" s="110"/>
+      <c r="K36" s="109" t="s">
         <v>63</v>
       </c>
-      <c r="L36" s="130"/>
+      <c r="L36" s="110"/>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B37" s="180"/>
-      <c r="D37" s="196" t="s">
+      <c r="B37" s="137"/>
+      <c r="D37" s="153" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="137" t="s">
+      <c r="E37" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="F37" s="138"/>
+      <c r="F37" s="77"/>
       <c r="H37" s="32"/>
-      <c r="I37" s="129">
+      <c r="I37" s="109">
         <v>25</v>
       </c>
-      <c r="J37" s="130"/>
-      <c r="K37" s="129" t="s">
+      <c r="J37" s="110"/>
+      <c r="K37" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="L37" s="130"/>
+      <c r="L37" s="110"/>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B38" s="180"/>
-      <c r="D38" s="197"/>
-      <c r="E38" s="140"/>
-      <c r="F38" s="141"/>
+      <c r="B38" s="137"/>
+      <c r="D38" s="154"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="80"/>
       <c r="H38" s="29"/>
-      <c r="I38" s="129">
+      <c r="I38" s="109">
         <v>30</v>
       </c>
-      <c r="J38" s="130"/>
-      <c r="K38" s="129" t="s">
+      <c r="J38" s="110"/>
+      <c r="K38" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="L38" s="130"/>
+      <c r="L38" s="110"/>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B39" s="180"/>
-      <c r="D39" s="198"/>
-      <c r="E39" s="142"/>
+      <c r="B39" s="137"/>
+      <c r="D39" s="155"/>
+      <c r="E39" s="81"/>
       <c r="F39" s="72"/>
       <c r="H39" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="I39" s="129" t="s">
+      <c r="I39" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="J39" s="130"/>
-      <c r="K39" s="129" t="s">
+      <c r="J39" s="110"/>
+      <c r="K39" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="L39" s="130"/>
+      <c r="L39" s="110"/>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B40" s="32"/>
-      <c r="D40" s="199" t="s">
+      <c r="D40" s="156" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="137" t="s">
+      <c r="E40" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="F40" s="138"/>
-      <c r="H40" s="180"/>
-      <c r="I40" s="200" t="s">
+      <c r="F40" s="77"/>
+      <c r="H40" s="137"/>
+      <c r="I40" s="157" t="s">
         <v>70</v>
       </c>
-      <c r="J40" s="130"/>
-      <c r="K40" s="129" t="s">
+      <c r="J40" s="110"/>
+      <c r="K40" s="109" t="s">
         <v>71</v>
       </c>
-      <c r="L40" s="130"/>
+      <c r="L40" s="110"/>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B41" s="32"/>
-      <c r="D41" s="201"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="141"/>
-      <c r="H41" s="180"/>
-      <c r="I41" s="129" t="s">
+      <c r="D41" s="158"/>
+      <c r="E41" s="78"/>
+      <c r="F41" s="80"/>
+      <c r="H41" s="137"/>
+      <c r="I41" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="J41" s="130"/>
-      <c r="K41" s="129" t="s">
+      <c r="J41" s="110"/>
+      <c r="K41" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="L41" s="130"/>
+      <c r="L41" s="110"/>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B42" s="29"/>
-      <c r="D42" s="202"/>
-      <c r="E42" s="142"/>
+      <c r="D42" s="159"/>
+      <c r="E42" s="81"/>
       <c r="F42" s="72"/>
       <c r="H42" s="29"/>
-      <c r="I42" s="129" t="s">
+      <c r="I42" s="109" t="s">
         <v>74</v>
       </c>
-      <c r="J42" s="130"/>
-      <c r="K42" s="129" t="s">
+      <c r="J42" s="110"/>
+      <c r="K42" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="L42" s="130"/>
+      <c r="L42" s="110"/>
     </row>
     <row r="44" customHeight="1" spans="2:12">
-      <c r="B44" s="171" t="s">
+      <c r="B44" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C44" s="175"/>
-      <c r="D44" s="175"/>
-      <c r="E44" s="175"/>
-      <c r="F44" s="175"/>
-      <c r="G44" s="175"/>
-      <c r="H44" s="175"/>
-      <c r="I44" s="175"/>
-      <c r="J44" s="175"/>
-      <c r="K44" s="175"/>
-      <c r="L44" s="176"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="4"/>
     </row>
     <row r="45" ht="10" customHeight="1"/>
     <row r="46" customHeight="1" spans="2:12">
@@ -10704,92 +10669,92 @@
     </row>
     <row r="47" ht="10" customHeight="1"/>
     <row r="48" customHeight="1" spans="2:12">
-      <c r="B48" s="171" t="s">
+      <c r="B48" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C48" s="175"/>
-      <c r="D48" s="175"/>
-      <c r="E48" s="175"/>
-      <c r="F48" s="175"/>
-      <c r="G48" s="175"/>
-      <c r="H48" s="175"/>
-      <c r="I48" s="175"/>
-      <c r="J48" s="175"/>
-      <c r="K48" s="175"/>
-      <c r="L48" s="176"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="4"/>
     </row>
     <row r="49" ht="10" customHeight="1"/>
     <row r="50" customHeight="1" spans="2:12">
-      <c r="B50" s="129" t="s">
+      <c r="B50" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="130"/>
-      <c r="D50" s="203" t="s">
+      <c r="C50" s="110"/>
+      <c r="D50" s="160" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="204"/>
-      <c r="F50" s="205"/>
-      <c r="H50" s="206" t="s">
+      <c r="E50" s="161"/>
+      <c r="F50" s="162"/>
+      <c r="H50" s="163" t="s">
         <v>81</v>
       </c>
-      <c r="I50" s="207"/>
-      <c r="J50" s="207"/>
-      <c r="K50" s="207"/>
-      <c r="L50" s="208"/>
+      <c r="I50" s="164"/>
+      <c r="J50" s="164"/>
+      <c r="K50" s="164"/>
+      <c r="L50" s="165"/>
     </row>
     <row r="51" customHeight="1" spans="2:12">
-      <c r="B51" s="129" t="s">
+      <c r="B51" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="130"/>
-      <c r="D51" s="203" t="s">
+      <c r="C51" s="110"/>
+      <c r="D51" s="160" t="s">
         <v>82</v>
       </c>
-      <c r="E51" s="204"/>
-      <c r="F51" s="205"/>
-      <c r="H51" s="206" t="s">
+      <c r="E51" s="161"/>
+      <c r="F51" s="162"/>
+      <c r="H51" s="163" t="s">
         <v>83</v>
       </c>
-      <c r="I51" s="207"/>
-      <c r="J51" s="207"/>
-      <c r="K51" s="207"/>
-      <c r="L51" s="208"/>
+      <c r="I51" s="164"/>
+      <c r="J51" s="164"/>
+      <c r="K51" s="164"/>
+      <c r="L51" s="165"/>
     </row>
     <row r="52" customHeight="1" spans="2:12">
-      <c r="B52" s="129" t="s">
+      <c r="B52" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="C52" s="130"/>
-      <c r="D52" s="209" t="s">
+      <c r="C52" s="110"/>
+      <c r="D52" s="166" t="s">
         <v>80</v>
       </c>
-      <c r="E52" s="210"/>
-      <c r="F52" s="211"/>
-      <c r="H52" s="212" t="s">
+      <c r="E52" s="167"/>
+      <c r="F52" s="168"/>
+      <c r="H52" s="169" t="s">
         <v>85</v>
       </c>
-      <c r="I52" s="213"/>
-      <c r="J52" s="213"/>
-      <c r="K52" s="213"/>
-      <c r="L52" s="214"/>
+      <c r="I52" s="170"/>
+      <c r="J52" s="170"/>
+      <c r="K52" s="170"/>
+      <c r="L52" s="171"/>
     </row>
     <row r="53" customHeight="1" spans="2:12">
-      <c r="B53" s="129" t="s">
+      <c r="B53" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="C53" s="130"/>
-      <c r="D53" s="209" t="s">
+      <c r="C53" s="110"/>
+      <c r="D53" s="166" t="s">
         <v>82</v>
       </c>
-      <c r="E53" s="210"/>
-      <c r="F53" s="211"/>
-      <c r="H53" s="212" t="s">
+      <c r="E53" s="167"/>
+      <c r="F53" s="168"/>
+      <c r="H53" s="169" t="s">
         <v>86</v>
       </c>
-      <c r="I53" s="213"/>
-      <c r="J53" s="213"/>
-      <c r="K53" s="213"/>
-      <c r="L53" s="214"/>
+      <c r="I53" s="170"/>
+      <c r="J53" s="170"/>
+      <c r="K53" s="170"/>
+      <c r="L53" s="171"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
@@ -10933,33 +10898,33 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="4"/>
-      <c r="S4" s="137" t="s">
+      <c r="S4" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="T4" s="138"/>
+      <c r="T4" s="77"/>
     </row>
     <row r="5" s="74" customFormat="1" ht="30" customHeight="1" spans="2:20">
-      <c r="B5" s="139" t="s">
+      <c r="B5" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="139"/>
-      <c r="F5" s="139"/>
-      <c r="H5" s="139" t="s">
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="H5" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="I5" s="139"/>
-      <c r="J5" s="139"/>
-      <c r="K5" s="139"/>
-      <c r="L5" s="139"/>
-      <c r="M5" s="139"/>
-      <c r="N5" s="139"/>
-      <c r="O5" s="139"/>
-      <c r="P5" s="139"/>
-      <c r="Q5" s="139"/>
-      <c r="S5" s="140"/>
-      <c r="T5" s="141"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="80"/>
     </row>
     <row r="6" s="74" customFormat="1" customHeight="1" spans="2:20">
       <c r="B6" s="2" t="s">
@@ -10981,33 +10946,33 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="4"/>
-      <c r="S6" s="142"/>
+      <c r="S6" s="81"/>
       <c r="T6" s="72"/>
     </row>
     <row r="7" s="74" customFormat="1" ht="30" customHeight="1" spans="2:20">
-      <c r="B7" s="139" t="s">
+      <c r="B7" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="139"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="139"/>
-      <c r="F7" s="139"/>
-      <c r="H7" s="139" t="s">
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="H7" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="139"/>
-      <c r="J7" s="139"/>
-      <c r="K7" s="139"/>
-      <c r="L7" s="139"/>
-      <c r="M7" s="139"/>
-      <c r="N7" s="139"/>
-      <c r="O7" s="139"/>
-      <c r="P7" s="139"/>
-      <c r="Q7" s="139"/>
-      <c r="S7" s="139" t="s">
+      <c r="I7" s="117"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="117"/>
+      <c r="L7" s="117"/>
+      <c r="M7" s="117"/>
+      <c r="N7" s="117"/>
+      <c r="O7" s="117"/>
+      <c r="P7" s="117"/>
+      <c r="Q7" s="117"/>
+      <c r="S7" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="T7" s="139"/>
+      <c r="T7" s="117"/>
     </row>
     <row r="8" s="74" customFormat="1" customHeight="1" spans="2:20">
       <c r="B8" s="2" t="s">
@@ -11029,33 +10994,33 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="4"/>
-      <c r="S8" s="137" t="s">
+      <c r="S8" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="T8" s="138"/>
+      <c r="T8" s="77"/>
     </row>
     <row r="9" s="74" customFormat="1" ht="30" customHeight="1" spans="2:20">
-      <c r="B9" s="139" t="s">
+      <c r="B9" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="139"/>
-      <c r="D9" s="139"/>
-      <c r="E9" s="139"/>
-      <c r="F9" s="139"/>
-      <c r="H9" s="139" t="s">
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="H9" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="I9" s="139"/>
-      <c r="J9" s="139"/>
-      <c r="K9" s="139"/>
-      <c r="L9" s="139"/>
-      <c r="M9" s="139"/>
-      <c r="N9" s="139"/>
-      <c r="O9" s="139"/>
-      <c r="P9" s="139"/>
-      <c r="Q9" s="139"/>
-      <c r="S9" s="140"/>
-      <c r="T9" s="141"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="117"/>
+      <c r="O9" s="117"/>
+      <c r="P9" s="117"/>
+      <c r="Q9" s="117"/>
+      <c r="S9" s="78"/>
+      <c r="T9" s="80"/>
     </row>
     <row r="10" s="74" customFormat="1" customHeight="1" spans="2:20">
       <c r="B10" s="2" t="s">
@@ -11065,642 +11030,632 @@
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="4"/>
-      <c r="H10" s="143" t="s">
+      <c r="H10" s="118" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="144"/>
-      <c r="J10" s="139" t="s">
+      <c r="I10" s="119"/>
+      <c r="J10" s="117" t="s">
         <v>99</v>
       </c>
-      <c r="K10" s="145" t="s">
+      <c r="K10" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="L10" s="146"/>
-      <c r="M10" s="146"/>
-      <c r="N10" s="146"/>
-      <c r="O10" s="146"/>
-      <c r="P10" s="146"/>
-      <c r="Q10" s="147"/>
-      <c r="S10" s="140"/>
-      <c r="T10" s="141"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="122"/>
+      <c r="S10" s="78"/>
+      <c r="T10" s="80"/>
     </row>
     <row r="11" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B11" s="148"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="148"/>
-      <c r="E11" s="148"/>
-      <c r="F11" s="148"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="139"/>
-      <c r="S11" s="140"/>
-      <c r="T11" s="141"/>
+      <c r="H11" s="123"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="117"/>
+      <c r="S11" s="78"/>
+      <c r="T11" s="80"/>
     </row>
     <row r="12" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B12" s="139" t="s">
+      <c r="B12" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="139"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="139"/>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="139"/>
-      <c r="K12" s="145" t="s">
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="117"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="120" t="s">
         <v>101</v>
       </c>
-      <c r="L12" s="146"/>
-      <c r="M12" s="146"/>
-      <c r="N12" s="146"/>
-      <c r="O12" s="146"/>
-      <c r="P12" s="146"/>
-      <c r="Q12" s="147"/>
-      <c r="S12" s="140"/>
-      <c r="T12" s="141"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="122"/>
+      <c r="S12" s="78"/>
+      <c r="T12" s="80"/>
     </row>
     <row r="13" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B13" s="139"/>
-      <c r="C13" s="139"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="139"/>
-      <c r="H13" s="149"/>
-      <c r="I13" s="150"/>
-      <c r="J13" s="139"/>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
+      <c r="H13" s="123"/>
+      <c r="I13" s="124"/>
+      <c r="J13" s="117"/>
+      <c r="S13" s="78"/>
+      <c r="T13" s="80"/>
     </row>
     <row r="14" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B14" s="139"/>
-      <c r="C14" s="139"/>
-      <c r="D14" s="139"/>
-      <c r="E14" s="139"/>
-      <c r="F14" s="139"/>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="139"/>
-      <c r="K14" s="145" t="s">
+      <c r="B14" s="117"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
+      <c r="H14" s="123"/>
+      <c r="I14" s="124"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="120" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="146"/>
-      <c r="M14" s="146"/>
-      <c r="N14" s="146"/>
-      <c r="O14" s="146"/>
-      <c r="P14" s="146"/>
-      <c r="Q14" s="147"/>
-      <c r="S14" s="140"/>
-      <c r="T14" s="141"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="122"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="80"/>
     </row>
     <row r="15" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="139"/>
-      <c r="S15" s="140"/>
-      <c r="T15" s="141"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="H15" s="123"/>
+      <c r="I15" s="124"/>
+      <c r="J15" s="117"/>
+      <c r="S15" s="78"/>
+      <c r="T15" s="80"/>
     </row>
     <row r="16" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B16" s="139"/>
-      <c r="C16" s="139"/>
-      <c r="D16" s="139"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="139"/>
-      <c r="H16" s="149"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="139"/>
-      <c r="K16" s="145" t="s">
+      <c r="B16" s="117"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="H16" s="123"/>
+      <c r="I16" s="124"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="120" t="s">
         <v>103</v>
       </c>
-      <c r="L16" s="146"/>
-      <c r="M16" s="146"/>
-      <c r="N16" s="146"/>
-      <c r="O16" s="146"/>
-      <c r="P16" s="146"/>
-      <c r="Q16" s="147"/>
-      <c r="S16" s="140"/>
-      <c r="T16" s="141"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="122"/>
+      <c r="S16" s="78"/>
+      <c r="T16" s="80"/>
     </row>
     <row r="17" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B17" s="139"/>
-      <c r="C17" s="139"/>
-      <c r="D17" s="139"/>
-      <c r="E17" s="139"/>
-      <c r="F17" s="139"/>
-      <c r="H17" s="149"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="139"/>
-      <c r="S17" s="140"/>
-      <c r="T17" s="141"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="H17" s="123"/>
+      <c r="I17" s="124"/>
+      <c r="J17" s="117"/>
+      <c r="S17" s="78"/>
+      <c r="T17" s="80"/>
     </row>
     <row r="18" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B18" s="139"/>
-      <c r="C18" s="139"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="139"/>
-      <c r="F18" s="139"/>
-      <c r="H18" s="149"/>
-      <c r="I18" s="150"/>
-      <c r="J18" s="139"/>
-      <c r="K18" s="145" t="s">
+      <c r="B18" s="117"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="120" t="s">
         <v>104</v>
       </c>
-      <c r="L18" s="146"/>
-      <c r="M18" s="146"/>
-      <c r="N18" s="146"/>
-      <c r="O18" s="146"/>
-      <c r="P18" s="146"/>
-      <c r="Q18" s="147"/>
-      <c r="S18" s="140"/>
-      <c r="T18" s="141"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="122"/>
+      <c r="S18" s="78"/>
+      <c r="T18" s="80"/>
     </row>
     <row r="19" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="H19" s="149"/>
-      <c r="I19" s="150"/>
-      <c r="J19" s="139"/>
-      <c r="S19" s="140"/>
-      <c r="T19" s="141"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="124"/>
+      <c r="J19" s="117"/>
+      <c r="S19" s="78"/>
+      <c r="T19" s="80"/>
     </row>
     <row r="20" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="H20" s="149"/>
-      <c r="I20" s="150"/>
-      <c r="J20" s="139"/>
-      <c r="K20" s="145" t="s">
+      <c r="B20" s="117"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="120" t="s">
         <v>105</v>
       </c>
-      <c r="L20" s="146"/>
-      <c r="M20" s="146"/>
-      <c r="N20" s="146"/>
-      <c r="O20" s="146"/>
-      <c r="P20" s="146"/>
-      <c r="Q20" s="147"/>
-      <c r="S20" s="140"/>
-      <c r="T20" s="141"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="122"/>
+      <c r="S20" s="78"/>
+      <c r="T20" s="80"/>
     </row>
     <row r="21" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B21" s="139"/>
-      <c r="C21" s="139"/>
-      <c r="D21" s="139"/>
-      <c r="E21" s="139"/>
-      <c r="F21" s="139"/>
-      <c r="H21" s="149"/>
-      <c r="I21" s="150"/>
-      <c r="J21" s="139"/>
-      <c r="S21" s="140"/>
-      <c r="T21" s="141"/>
+      <c r="B21" s="117"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="117"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="124"/>
+      <c r="J21" s="117"/>
+      <c r="S21" s="78"/>
+      <c r="T21" s="80"/>
     </row>
     <row r="22" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B22" s="139"/>
-      <c r="C22" s="139"/>
-      <c r="D22" s="139"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="139"/>
-      <c r="H22" s="149"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="139"/>
-      <c r="K22" s="145" t="s">
+      <c r="B22" s="117"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="H22" s="123"/>
+      <c r="I22" s="124"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="120" t="s">
         <v>106</v>
       </c>
-      <c r="L22" s="146"/>
-      <c r="M22" s="146"/>
-      <c r="N22" s="146"/>
-      <c r="O22" s="146"/>
-      <c r="P22" s="146"/>
-      <c r="Q22" s="147"/>
-      <c r="S22" s="140"/>
-      <c r="T22" s="141"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="121"/>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="122"/>
+      <c r="S22" s="78"/>
+      <c r="T22" s="80"/>
     </row>
     <row r="23" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B23" s="139"/>
-      <c r="C23" s="139"/>
-      <c r="D23" s="139"/>
-      <c r="E23" s="139"/>
-      <c r="F23" s="139"/>
-      <c r="H23" s="149"/>
-      <c r="I23" s="150"/>
-      <c r="J23" s="139"/>
-      <c r="S23" s="140"/>
-      <c r="T23" s="141"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="124"/>
+      <c r="J23" s="117"/>
+      <c r="S23" s="78"/>
+      <c r="T23" s="80"/>
     </row>
     <row r="24" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B24" s="139"/>
-      <c r="C24" s="139"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="139"/>
-      <c r="F24" s="139"/>
-      <c r="H24" s="151"/>
-      <c r="I24" s="152"/>
-      <c r="J24" s="139"/>
-      <c r="K24" s="145" t="s">
+      <c r="B24" s="117"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="126"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="120" t="s">
         <v>107</v>
       </c>
-      <c r="L24" s="146"/>
-      <c r="M24" s="146"/>
-      <c r="N24" s="146"/>
-      <c r="O24" s="146"/>
-      <c r="P24" s="146"/>
-      <c r="Q24" s="147"/>
-      <c r="S24" s="140"/>
-      <c r="T24" s="141"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="121"/>
+      <c r="Q24" s="122"/>
+      <c r="S24" s="78"/>
+      <c r="T24" s="80"/>
     </row>
     <row r="25" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B25" s="139"/>
-      <c r="C25" s="139"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="S25" s="140"/>
-      <c r="T25" s="141"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="117"/>
+      <c r="S25" s="78"/>
+      <c r="T25" s="80"/>
     </row>
     <row r="26" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B26" s="139"/>
-      <c r="C26" s="139"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="H26" s="153" t="s">
+      <c r="B26" s="117"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="H26" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="I26" s="154"/>
-      <c r="J26" s="139" t="s">
+      <c r="I26" s="128"/>
+      <c r="J26" s="117" t="s">
         <v>99</v>
       </c>
-      <c r="K26" s="155" t="s">
+      <c r="K26" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="L26" s="156"/>
-      <c r="M26" s="156"/>
-      <c r="N26" s="156"/>
-      <c r="O26" s="156"/>
-      <c r="P26" s="156"/>
-      <c r="Q26" s="157"/>
-      <c r="S26" s="140"/>
-      <c r="T26" s="141"/>
+      <c r="L26" s="130"/>
+      <c r="M26" s="130"/>
+      <c r="N26" s="130"/>
+      <c r="O26" s="130"/>
+      <c r="P26" s="130"/>
+      <c r="Q26" s="131"/>
+      <c r="S26" s="78"/>
+      <c r="T26" s="80"/>
     </row>
     <row r="27" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B27" s="139"/>
-      <c r="C27" s="139"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="H27" s="158"/>
-      <c r="I27" s="159"/>
-      <c r="J27" s="139"/>
-      <c r="S27" s="140"/>
-      <c r="T27" s="141"/>
+      <c r="B27" s="117"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="133"/>
+      <c r="J27" s="117"/>
+      <c r="S27" s="78"/>
+      <c r="T27" s="80"/>
     </row>
     <row r="28" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B28" s="139"/>
-      <c r="C28" s="139"/>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="H28" s="158"/>
-      <c r="I28" s="159"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="155" t="s">
+      <c r="B28" s="117"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="117"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="133"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="129" t="s">
         <v>110</v>
       </c>
-      <c r="L28" s="156"/>
-      <c r="M28" s="156"/>
-      <c r="N28" s="156"/>
-      <c r="O28" s="156"/>
-      <c r="P28" s="156"/>
-      <c r="Q28" s="157"/>
-      <c r="S28" s="140"/>
-      <c r="T28" s="141"/>
+      <c r="L28" s="130"/>
+      <c r="M28" s="130"/>
+      <c r="N28" s="130"/>
+      <c r="O28" s="130"/>
+      <c r="P28" s="130"/>
+      <c r="Q28" s="131"/>
+      <c r="S28" s="78"/>
+      <c r="T28" s="80"/>
     </row>
     <row r="29" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B29" s="139"/>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="H29" s="158"/>
-      <c r="I29" s="159"/>
-      <c r="J29" s="139"/>
-      <c r="S29" s="140"/>
-      <c r="T29" s="141"/>
+      <c r="B29" s="117"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="117"/>
+      <c r="H29" s="132"/>
+      <c r="I29" s="133"/>
+      <c r="J29" s="117"/>
+      <c r="S29" s="78"/>
+      <c r="T29" s="80"/>
     </row>
     <row r="30" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B30" s="139"/>
-      <c r="C30" s="139"/>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
-      <c r="H30" s="158"/>
-      <c r="I30" s="159"/>
-      <c r="J30" s="139"/>
-      <c r="K30" s="155" t="s">
+      <c r="B30" s="117"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="H30" s="132"/>
+      <c r="I30" s="133"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="129" t="s">
         <v>111</v>
       </c>
-      <c r="L30" s="156"/>
-      <c r="M30" s="156"/>
-      <c r="N30" s="156"/>
-      <c r="O30" s="156"/>
-      <c r="P30" s="156"/>
-      <c r="Q30" s="157"/>
-      <c r="S30" s="140"/>
-      <c r="T30" s="141"/>
+      <c r="L30" s="130"/>
+      <c r="M30" s="130"/>
+      <c r="N30" s="130"/>
+      <c r="O30" s="130"/>
+      <c r="P30" s="130"/>
+      <c r="Q30" s="131"/>
+      <c r="S30" s="78"/>
+      <c r="T30" s="80"/>
     </row>
     <row r="31" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B31" s="139"/>
-      <c r="C31" s="139"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="H31" s="158"/>
-      <c r="I31" s="159"/>
-      <c r="J31" s="139"/>
-      <c r="S31" s="140"/>
-      <c r="T31" s="141"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="H31" s="132"/>
+      <c r="I31" s="133"/>
+      <c r="J31" s="117"/>
+      <c r="S31" s="78"/>
+      <c r="T31" s="80"/>
     </row>
     <row r="32" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B32" s="139"/>
-      <c r="C32" s="139"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
-      <c r="H32" s="158"/>
-      <c r="I32" s="159"/>
-      <c r="J32" s="139"/>
-      <c r="K32" s="155" t="s">
+      <c r="B32" s="117"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="H32" s="132"/>
+      <c r="I32" s="133"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="129" t="s">
         <v>112</v>
       </c>
-      <c r="L32" s="156"/>
-      <c r="M32" s="156"/>
-      <c r="N32" s="156"/>
-      <c r="O32" s="156"/>
-      <c r="P32" s="156"/>
-      <c r="Q32" s="157"/>
-      <c r="S32" s="140"/>
-      <c r="T32" s="141"/>
+      <c r="L32" s="130"/>
+      <c r="M32" s="130"/>
+      <c r="N32" s="130"/>
+      <c r="O32" s="130"/>
+      <c r="P32" s="130"/>
+      <c r="Q32" s="131"/>
+      <c r="S32" s="78"/>
+      <c r="T32" s="80"/>
     </row>
     <row r="33" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B33" s="139"/>
-      <c r="C33" s="139"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="H33" s="158"/>
-      <c r="I33" s="159"/>
-      <c r="J33" s="139"/>
-      <c r="S33" s="140"/>
-      <c r="T33" s="141"/>
+      <c r="B33" s="117"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="117"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="133"/>
+      <c r="J33" s="117"/>
+      <c r="S33" s="78"/>
+      <c r="T33" s="80"/>
     </row>
     <row r="34" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B34" s="139"/>
-      <c r="C34" s="139"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="139"/>
-      <c r="F34" s="139"/>
-      <c r="H34" s="158"/>
-      <c r="I34" s="159"/>
-      <c r="J34" s="139"/>
-      <c r="K34" s="155" t="s">
+      <c r="B34" s="117"/>
+      <c r="C34" s="117"/>
+      <c r="D34" s="117"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="117"/>
+      <c r="H34" s="132"/>
+      <c r="I34" s="133"/>
+      <c r="J34" s="117"/>
+      <c r="K34" s="129" t="s">
         <v>113</v>
       </c>
-      <c r="L34" s="156"/>
-      <c r="M34" s="156"/>
-      <c r="N34" s="156"/>
-      <c r="O34" s="156"/>
-      <c r="P34" s="156"/>
-      <c r="Q34" s="157"/>
-      <c r="S34" s="140"/>
-      <c r="T34" s="141"/>
+      <c r="L34" s="130"/>
+      <c r="M34" s="130"/>
+      <c r="N34" s="130"/>
+      <c r="O34" s="130"/>
+      <c r="P34" s="130"/>
+      <c r="Q34" s="131"/>
+      <c r="S34" s="78"/>
+      <c r="T34" s="80"/>
     </row>
     <row r="35" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B35" s="139"/>
-      <c r="C35" s="139"/>
-      <c r="D35" s="139"/>
-      <c r="E35" s="139"/>
-      <c r="F35" s="139"/>
-      <c r="H35" s="158"/>
-      <c r="I35" s="159"/>
-      <c r="J35" s="139"/>
-      <c r="S35" s="140"/>
-      <c r="T35" s="141"/>
+      <c r="B35" s="117"/>
+      <c r="C35" s="117"/>
+      <c r="D35" s="117"/>
+      <c r="E35" s="117"/>
+      <c r="F35" s="117"/>
+      <c r="H35" s="132"/>
+      <c r="I35" s="133"/>
+      <c r="J35" s="117"/>
+      <c r="S35" s="78"/>
+      <c r="T35" s="80"/>
     </row>
     <row r="36" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B36" s="139"/>
-      <c r="C36" s="139"/>
-      <c r="D36" s="139"/>
-      <c r="E36" s="139"/>
-      <c r="F36" s="139"/>
-      <c r="H36" s="158"/>
-      <c r="I36" s="159"/>
-      <c r="J36" s="139"/>
-      <c r="K36" s="155" t="s">
+      <c r="B36" s="117"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="117"/>
+      <c r="H36" s="132"/>
+      <c r="I36" s="133"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="129" t="s">
         <v>114</v>
       </c>
-      <c r="L36" s="156"/>
-      <c r="M36" s="156"/>
-      <c r="N36" s="156"/>
-      <c r="O36" s="156"/>
-      <c r="P36" s="156"/>
-      <c r="Q36" s="157"/>
-      <c r="S36" s="140"/>
-      <c r="T36" s="141"/>
+      <c r="L36" s="130"/>
+      <c r="M36" s="130"/>
+      <c r="N36" s="130"/>
+      <c r="O36" s="130"/>
+      <c r="P36" s="130"/>
+      <c r="Q36" s="131"/>
+      <c r="S36" s="78"/>
+      <c r="T36" s="80"/>
     </row>
     <row r="37" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B37" s="139"/>
-      <c r="C37" s="139"/>
-      <c r="D37" s="139"/>
-      <c r="E37" s="139"/>
-      <c r="F37" s="139"/>
-      <c r="H37" s="158"/>
-      <c r="I37" s="159"/>
-      <c r="J37" s="139"/>
-      <c r="S37" s="140"/>
-      <c r="T37" s="141"/>
+      <c r="B37" s="117"/>
+      <c r="C37" s="117"/>
+      <c r="D37" s="117"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="117"/>
+      <c r="H37" s="132"/>
+      <c r="I37" s="133"/>
+      <c r="J37" s="117"/>
+      <c r="S37" s="78"/>
+      <c r="T37" s="80"/>
     </row>
     <row r="38" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B38" s="139"/>
-      <c r="C38" s="139"/>
-      <c r="D38" s="139"/>
-      <c r="E38" s="139"/>
-      <c r="F38" s="139"/>
-      <c r="H38" s="158"/>
-      <c r="I38" s="159"/>
-      <c r="J38" s="139"/>
-      <c r="K38" s="155" t="s">
+      <c r="B38" s="117"/>
+      <c r="C38" s="117"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="117"/>
+      <c r="H38" s="132"/>
+      <c r="I38" s="133"/>
+      <c r="J38" s="117"/>
+      <c r="K38" s="129" t="s">
         <v>115</v>
       </c>
-      <c r="L38" s="156"/>
-      <c r="M38" s="156"/>
-      <c r="N38" s="156"/>
-      <c r="O38" s="156"/>
-      <c r="P38" s="156"/>
-      <c r="Q38" s="157"/>
-      <c r="S38" s="140"/>
-      <c r="T38" s="141"/>
+      <c r="L38" s="130"/>
+      <c r="M38" s="130"/>
+      <c r="N38" s="130"/>
+      <c r="O38" s="130"/>
+      <c r="P38" s="130"/>
+      <c r="Q38" s="131"/>
+      <c r="S38" s="78"/>
+      <c r="T38" s="80"/>
     </row>
     <row r="39" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B39" s="139"/>
-      <c r="C39" s="139"/>
-      <c r="D39" s="139"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="H39" s="158"/>
-      <c r="I39" s="159"/>
-      <c r="J39" s="139"/>
-      <c r="S39" s="140"/>
-      <c r="T39" s="141"/>
+      <c r="B39" s="117"/>
+      <c r="C39" s="117"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="117"/>
+      <c r="H39" s="132"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="117"/>
+      <c r="S39" s="78"/>
+      <c r="T39" s="80"/>
     </row>
     <row r="40" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B40" s="139"/>
-      <c r="C40" s="139"/>
-      <c r="D40" s="139"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="H40" s="158"/>
-      <c r="I40" s="159"/>
-      <c r="J40" s="139"/>
-      <c r="K40" s="155" t="s">
+      <c r="B40" s="117"/>
+      <c r="C40" s="117"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="117"/>
+      <c r="H40" s="132"/>
+      <c r="I40" s="133"/>
+      <c r="J40" s="117"/>
+      <c r="K40" s="129" t="s">
         <v>116</v>
       </c>
-      <c r="L40" s="156"/>
-      <c r="M40" s="156"/>
-      <c r="N40" s="156"/>
-      <c r="O40" s="156"/>
-      <c r="P40" s="156"/>
-      <c r="Q40" s="157"/>
-      <c r="S40" s="140"/>
-      <c r="T40" s="141"/>
+      <c r="L40" s="130"/>
+      <c r="M40" s="130"/>
+      <c r="N40" s="130"/>
+      <c r="O40" s="130"/>
+      <c r="P40" s="130"/>
+      <c r="Q40" s="131"/>
+      <c r="S40" s="78"/>
+      <c r="T40" s="80"/>
     </row>
     <row r="41" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B41" s="139"/>
-      <c r="C41" s="139"/>
-      <c r="D41" s="139"/>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
-      <c r="H41" s="158"/>
-      <c r="I41" s="159"/>
-      <c r="J41" s="139"/>
-      <c r="S41" s="140"/>
-      <c r="T41" s="141"/>
+      <c r="B41" s="117"/>
+      <c r="C41" s="117"/>
+      <c r="D41" s="117"/>
+      <c r="E41" s="117"/>
+      <c r="F41" s="117"/>
+      <c r="H41" s="132"/>
+      <c r="I41" s="133"/>
+      <c r="J41" s="117"/>
+      <c r="S41" s="78"/>
+      <c r="T41" s="80"/>
     </row>
     <row r="42" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B42" s="139"/>
-      <c r="C42" s="139"/>
-      <c r="D42" s="139"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="H42" s="158"/>
-      <c r="I42" s="159"/>
-      <c r="J42" s="139"/>
-      <c r="K42" s="155" t="s">
+      <c r="B42" s="117"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="117"/>
+      <c r="E42" s="117"/>
+      <c r="F42" s="117"/>
+      <c r="H42" s="132"/>
+      <c r="I42" s="133"/>
+      <c r="J42" s="117"/>
+      <c r="K42" s="129" t="s">
         <v>117</v>
       </c>
-      <c r="L42" s="156"/>
-      <c r="M42" s="156"/>
-      <c r="N42" s="156"/>
-      <c r="O42" s="156"/>
-      <c r="P42" s="156"/>
-      <c r="Q42" s="157"/>
-      <c r="S42" s="140"/>
-      <c r="T42" s="141"/>
+      <c r="L42" s="130"/>
+      <c r="M42" s="130"/>
+      <c r="N42" s="130"/>
+      <c r="O42" s="130"/>
+      <c r="P42" s="130"/>
+      <c r="Q42" s="131"/>
+      <c r="S42" s="78"/>
+      <c r="T42" s="80"/>
     </row>
     <row r="43" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B43" s="139"/>
-      <c r="C43" s="139"/>
-      <c r="D43" s="139"/>
-      <c r="E43" s="139"/>
-      <c r="F43" s="139"/>
-      <c r="H43" s="158"/>
-      <c r="I43" s="159"/>
-      <c r="J43" s="139"/>
-      <c r="S43" s="140"/>
-      <c r="T43" s="141"/>
+      <c r="B43" s="117"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="117"/>
+      <c r="F43" s="117"/>
+      <c r="H43" s="132"/>
+      <c r="I43" s="133"/>
+      <c r="J43" s="117"/>
+      <c r="S43" s="78"/>
+      <c r="T43" s="80"/>
     </row>
     <row r="44" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B44" s="139"/>
-      <c r="C44" s="139"/>
-      <c r="D44" s="139"/>
-      <c r="E44" s="139"/>
-      <c r="F44" s="139"/>
-      <c r="H44" s="158"/>
-      <c r="I44" s="159"/>
-      <c r="J44" s="139"/>
-      <c r="K44" s="155" t="s">
+      <c r="B44" s="117"/>
+      <c r="C44" s="117"/>
+      <c r="D44" s="117"/>
+      <c r="E44" s="117"/>
+      <c r="F44" s="117"/>
+      <c r="H44" s="132"/>
+      <c r="I44" s="133"/>
+      <c r="J44" s="117"/>
+      <c r="K44" s="129" t="s">
         <v>118</v>
       </c>
-      <c r="L44" s="156"/>
-      <c r="M44" s="156"/>
-      <c r="N44" s="156"/>
-      <c r="O44" s="156"/>
-      <c r="P44" s="156"/>
-      <c r="Q44" s="157"/>
-      <c r="S44" s="140"/>
-      <c r="T44" s="141"/>
+      <c r="L44" s="130"/>
+      <c r="M44" s="130"/>
+      <c r="N44" s="130"/>
+      <c r="O44" s="130"/>
+      <c r="P44" s="130"/>
+      <c r="Q44" s="131"/>
+      <c r="S44" s="78"/>
+      <c r="T44" s="80"/>
     </row>
     <row r="45" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B45" s="139"/>
-      <c r="C45" s="139"/>
-      <c r="D45" s="139"/>
-      <c r="E45" s="139"/>
-      <c r="F45" s="139"/>
-      <c r="H45" s="158"/>
-      <c r="I45" s="159"/>
-      <c r="J45" s="139"/>
-      <c r="S45" s="140"/>
-      <c r="T45" s="141"/>
+      <c r="B45" s="117"/>
+      <c r="C45" s="117"/>
+      <c r="D45" s="117"/>
+      <c r="E45" s="117"/>
+      <c r="F45" s="117"/>
+      <c r="H45" s="132"/>
+      <c r="I45" s="133"/>
+      <c r="J45" s="117"/>
+      <c r="S45" s="78"/>
+      <c r="T45" s="80"/>
     </row>
     <row r="46" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B46" s="139"/>
-      <c r="C46" s="139"/>
-      <c r="D46" s="139"/>
-      <c r="E46" s="139"/>
-      <c r="F46" s="139"/>
-      <c r="H46" s="160"/>
-      <c r="I46" s="161"/>
-      <c r="J46" s="139"/>
-      <c r="K46" s="155" t="s">
+      <c r="B46" s="117"/>
+      <c r="C46" s="117"/>
+      <c r="D46" s="117"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="117"/>
+      <c r="H46" s="134"/>
+      <c r="I46" s="135"/>
+      <c r="J46" s="117"/>
+      <c r="K46" s="129" t="s">
         <v>119</v>
       </c>
-      <c r="L46" s="156"/>
-      <c r="M46" s="156"/>
-      <c r="N46" s="156"/>
-      <c r="O46" s="156"/>
-      <c r="P46" s="156"/>
-      <c r="Q46" s="157"/>
-      <c r="S46" s="140"/>
-      <c r="T46" s="141"/>
+      <c r="L46" s="130"/>
+      <c r="M46" s="130"/>
+      <c r="N46" s="130"/>
+      <c r="O46" s="130"/>
+      <c r="P46" s="130"/>
+      <c r="Q46" s="131"/>
+      <c r="S46" s="78"/>
+      <c r="T46" s="80"/>
     </row>
     <row r="47" s="74" customFormat="1" ht="30" customHeight="1" spans="2:20">
-      <c r="B47" s="148"/>
-      <c r="C47" s="148"/>
-      <c r="D47" s="148"/>
-      <c r="E47" s="148"/>
-      <c r="F47" s="148"/>
-      <c r="H47" s="139" t="s">
+      <c r="H47" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="I47" s="139"/>
-      <c r="J47" s="139"/>
-      <c r="K47" s="139"/>
-      <c r="L47" s="139"/>
-      <c r="M47" s="139"/>
-      <c r="N47" s="139"/>
-      <c r="O47" s="139"/>
-      <c r="P47" s="139"/>
-      <c r="Q47" s="139"/>
-      <c r="S47" s="140"/>
-      <c r="T47" s="141"/>
+      <c r="I47" s="117"/>
+      <c r="J47" s="117"/>
+      <c r="K47" s="117"/>
+      <c r="L47" s="117"/>
+      <c r="M47" s="117"/>
+      <c r="N47" s="117"/>
+      <c r="O47" s="117"/>
+      <c r="P47" s="117"/>
+      <c r="Q47" s="117"/>
+      <c r="S47" s="78"/>
+      <c r="T47" s="80"/>
     </row>
     <row r="48" s="74" customFormat="1" customHeight="1" spans="2:20">
       <c r="B48" s="2" t="s">
@@ -11722,33 +11677,33 @@
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
       <c r="Q48" s="4"/>
-      <c r="S48" s="142"/>
+      <c r="S48" s="81"/>
       <c r="T48" s="72"/>
     </row>
     <row r="49" s="74" customFormat="1" ht="30" customHeight="1" spans="2:20">
-      <c r="B49" s="139" t="s">
+      <c r="B49" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="C49" s="139"/>
-      <c r="D49" s="139"/>
-      <c r="E49" s="139"/>
-      <c r="F49" s="139"/>
-      <c r="H49" s="139" t="s">
+      <c r="C49" s="117"/>
+      <c r="D49" s="117"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="117"/>
+      <c r="H49" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="I49" s="139"/>
-      <c r="J49" s="139"/>
-      <c r="K49" s="139"/>
-      <c r="L49" s="139"/>
-      <c r="M49" s="139"/>
-      <c r="N49" s="139"/>
-      <c r="O49" s="139"/>
-      <c r="P49" s="139"/>
-      <c r="Q49" s="139"/>
-      <c r="S49" s="139" t="s">
+      <c r="I49" s="117"/>
+      <c r="J49" s="117"/>
+      <c r="K49" s="117"/>
+      <c r="L49" s="117"/>
+      <c r="M49" s="117"/>
+      <c r="N49" s="117"/>
+      <c r="O49" s="117"/>
+      <c r="P49" s="117"/>
+      <c r="Q49" s="117"/>
+      <c r="S49" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="T49" s="139"/>
+      <c r="T49" s="117"/>
     </row>
     <row r="50" s="74" customFormat="1" customHeight="1" spans="2:20">
       <c r="B50" s="2" t="s">
@@ -11776,66 +11731,66 @@
       <c r="T50" s="4"/>
     </row>
     <row r="52" s="74" customFormat="1" customHeight="1" spans="2:20">
-      <c r="B52" s="162" t="s">
+      <c r="B52" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="C52" s="163"/>
-      <c r="D52" s="163"/>
-      <c r="E52" s="163"/>
-      <c r="F52" s="164"/>
-      <c r="H52" s="162" t="s">
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="31"/>
+      <c r="H52" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="I52" s="164"/>
+      <c r="I52" s="31"/>
       <c r="K52" s="75" t="s">
         <v>126</v>
       </c>
-      <c r="L52" s="163"/>
-      <c r="M52" s="163"/>
-      <c r="N52" s="163"/>
-      <c r="O52" s="163"/>
-      <c r="P52" s="163"/>
-      <c r="Q52" s="163"/>
-      <c r="R52" s="163"/>
-      <c r="S52" s="163"/>
-      <c r="T52" s="164"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="55"/>
+      <c r="N52" s="55"/>
+      <c r="O52" s="55"/>
+      <c r="P52" s="55"/>
+      <c r="Q52" s="55"/>
+      <c r="R52" s="55"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="31"/>
     </row>
     <row r="53" customHeight="1" spans="2:20">
-      <c r="B53" s="165"/>
-      <c r="C53" s="166"/>
-      <c r="D53" s="166"/>
-      <c r="E53" s="166"/>
-      <c r="F53" s="167"/>
-      <c r="H53" s="168"/>
-      <c r="I53" s="169"/>
-      <c r="K53" s="168"/>
-      <c r="L53" s="170"/>
-      <c r="M53" s="170"/>
-      <c r="N53" s="170"/>
-      <c r="O53" s="170"/>
-      <c r="P53" s="170"/>
-      <c r="Q53" s="170"/>
-      <c r="R53" s="170"/>
-      <c r="S53" s="170"/>
-      <c r="T53" s="169"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="91"/>
+      <c r="D53" s="91"/>
+      <c r="E53" s="91"/>
+      <c r="F53" s="34"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="36"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="56"/>
+      <c r="N53" s="56"/>
+      <c r="O53" s="56"/>
+      <c r="P53" s="56"/>
+      <c r="Q53" s="56"/>
+      <c r="R53" s="56"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="36"/>
     </row>
     <row r="54" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B54" s="165"/>
-      <c r="C54" s="166"/>
-      <c r="D54" s="166"/>
-      <c r="E54" s="166"/>
-      <c r="F54" s="167"/>
+      <c r="B54" s="33"/>
+      <c r="C54" s="91"/>
+      <c r="D54" s="91"/>
+      <c r="E54" s="91"/>
+      <c r="F54" s="34"/>
     </row>
     <row r="55" customHeight="1" spans="2:20">
-      <c r="B55" s="165"/>
-      <c r="C55" s="166"/>
-      <c r="D55" s="166"/>
-      <c r="E55" s="166"/>
-      <c r="F55" s="167"/>
-      <c r="H55" s="162" t="s">
+      <c r="B55" s="33"/>
+      <c r="C55" s="91"/>
+      <c r="D55" s="91"/>
+      <c r="E55" s="91"/>
+      <c r="F55" s="34"/>
+      <c r="H55" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="I55" s="164"/>
+      <c r="I55" s="31"/>
       <c r="K55" s="75" t="s">
         <v>128</v>
       </c>
@@ -11850,13 +11805,13 @@
       <c r="T55" s="77"/>
     </row>
     <row r="56" customHeight="1" spans="2:20">
-      <c r="B56" s="165"/>
-      <c r="C56" s="166"/>
-      <c r="D56" s="166"/>
-      <c r="E56" s="166"/>
-      <c r="F56" s="167"/>
-      <c r="H56" s="165"/>
-      <c r="I56" s="167"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="91"/>
+      <c r="D56" s="91"/>
+      <c r="E56" s="91"/>
+      <c r="F56" s="34"/>
+      <c r="H56" s="33"/>
+      <c r="I56" s="34"/>
       <c r="K56" s="78"/>
       <c r="L56" s="79"/>
       <c r="M56" s="79"/>
@@ -11869,13 +11824,13 @@
       <c r="T56" s="80"/>
     </row>
     <row r="57" customHeight="1" spans="2:20">
-      <c r="B57" s="165"/>
-      <c r="C57" s="166"/>
-      <c r="D57" s="166"/>
-      <c r="E57" s="166"/>
-      <c r="F57" s="167"/>
-      <c r="H57" s="168"/>
-      <c r="I57" s="169"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="91"/>
+      <c r="D57" s="91"/>
+      <c r="E57" s="91"/>
+      <c r="F57" s="34"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="36"/>
       <c r="K57" s="81"/>
       <c r="L57" s="82"/>
       <c r="M57" s="82"/>
@@ -11885,268 +11840,268 @@
       <c r="Q57" s="82"/>
       <c r="R57" s="82"/>
       <c r="S57" s="82"/>
-      <c r="T57" s="83"/>
+      <c r="T57" s="72"/>
     </row>
     <row r="58" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B58" s="165"/>
-      <c r="C58" s="166"/>
-      <c r="D58" s="166"/>
-      <c r="E58" s="166"/>
-      <c r="F58" s="167"/>
+      <c r="B58" s="33"/>
+      <c r="C58" s="91"/>
+      <c r="D58" s="91"/>
+      <c r="E58" s="91"/>
+      <c r="F58" s="34"/>
     </row>
     <row r="59" customHeight="1" spans="2:20">
-      <c r="B59" s="165"/>
-      <c r="C59" s="166"/>
-      <c r="D59" s="166"/>
-      <c r="E59" s="166"/>
-      <c r="F59" s="167"/>
-      <c r="H59" s="162" t="s">
+      <c r="B59" s="33"/>
+      <c r="C59" s="91"/>
+      <c r="D59" s="91"/>
+      <c r="E59" s="91"/>
+      <c r="F59" s="34"/>
+      <c r="H59" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="I59" s="164"/>
-      <c r="K59" s="171" t="s">
+      <c r="I59" s="31"/>
+      <c r="K59" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L59" s="172"/>
-      <c r="M59" s="171" t="s">
+      <c r="L59" s="4"/>
+      <c r="M59" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="N59" s="173"/>
-      <c r="O59" s="173"/>
-      <c r="P59" s="173"/>
-      <c r="Q59" s="173"/>
-      <c r="R59" s="173"/>
-      <c r="S59" s="173"/>
-      <c r="T59" s="172"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+      <c r="T59" s="4"/>
     </row>
     <row r="60" customHeight="1" spans="2:20">
-      <c r="B60" s="165"/>
-      <c r="C60" s="166"/>
-      <c r="D60" s="166"/>
-      <c r="E60" s="166"/>
-      <c r="F60" s="167"/>
-      <c r="H60" s="165"/>
-      <c r="I60" s="167"/>
-      <c r="K60" s="174" t="s">
+      <c r="B60" s="33"/>
+      <c r="C60" s="91"/>
+      <c r="D60" s="91"/>
+      <c r="E60" s="91"/>
+      <c r="F60" s="34"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="34"/>
+      <c r="K60" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="L60" s="172"/>
-      <c r="M60" s="174" t="s">
+      <c r="L60" s="4"/>
+      <c r="M60" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="N60" s="173"/>
-      <c r="O60" s="173"/>
-      <c r="P60" s="173"/>
-      <c r="Q60" s="173"/>
-      <c r="R60" s="173"/>
-      <c r="S60" s="173"/>
-      <c r="T60" s="172"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="4"/>
     </row>
     <row r="61" customHeight="1" spans="2:20">
-      <c r="B61" s="165"/>
-      <c r="C61" s="166"/>
-      <c r="D61" s="166"/>
-      <c r="E61" s="166"/>
-      <c r="F61" s="167"/>
-      <c r="H61" s="165"/>
-      <c r="I61" s="167"/>
-      <c r="K61" s="174" t="s">
+      <c r="B61" s="33"/>
+      <c r="C61" s="91"/>
+      <c r="D61" s="91"/>
+      <c r="E61" s="91"/>
+      <c r="F61" s="34"/>
+      <c r="H61" s="33"/>
+      <c r="I61" s="34"/>
+      <c r="K61" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="L61" s="172"/>
-      <c r="M61" s="174" t="s">
+      <c r="L61" s="4"/>
+      <c r="M61" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="N61" s="173"/>
-      <c r="O61" s="173"/>
-      <c r="P61" s="173"/>
-      <c r="Q61" s="173"/>
-      <c r="R61" s="173"/>
-      <c r="S61" s="173"/>
-      <c r="T61" s="172"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="4"/>
     </row>
     <row r="62" customHeight="1" spans="2:20">
-      <c r="B62" s="165"/>
-      <c r="C62" s="166"/>
-      <c r="D62" s="166"/>
-      <c r="E62" s="166"/>
-      <c r="F62" s="167"/>
-      <c r="H62" s="168"/>
-      <c r="I62" s="169"/>
-      <c r="K62" s="174" t="s">
+      <c r="B62" s="33"/>
+      <c r="C62" s="91"/>
+      <c r="D62" s="91"/>
+      <c r="E62" s="91"/>
+      <c r="F62" s="34"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="36"/>
+      <c r="K62" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="L62" s="172"/>
-      <c r="M62" s="171" t="s">
+      <c r="L62" s="4"/>
+      <c r="M62" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="N62" s="173"/>
-      <c r="O62" s="173"/>
-      <c r="P62" s="173"/>
-      <c r="Q62" s="173"/>
-      <c r="R62" s="173"/>
-      <c r="S62" s="173"/>
-      <c r="T62" s="172"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="4"/>
     </row>
     <row r="63" s="74" customFormat="1" ht="10" customHeight="1" spans="2:20">
-      <c r="B63" s="165"/>
-      <c r="C63" s="166"/>
-      <c r="D63" s="166"/>
-      <c r="E63" s="166"/>
-      <c r="F63" s="167"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="91"/>
+      <c r="D63" s="91"/>
+      <c r="E63" s="91"/>
+      <c r="F63" s="34"/>
     </row>
     <row r="64" customHeight="1" spans="2:20">
-      <c r="B64" s="165"/>
-      <c r="C64" s="166"/>
-      <c r="D64" s="166"/>
-      <c r="E64" s="166"/>
-      <c r="F64" s="167"/>
-      <c r="H64" s="162" t="s">
+      <c r="B64" s="33"/>
+      <c r="C64" s="91"/>
+      <c r="D64" s="91"/>
+      <c r="E64" s="91"/>
+      <c r="F64" s="34"/>
+      <c r="H64" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="I64" s="164"/>
-      <c r="K64" s="171" t="s">
+      <c r="I64" s="31"/>
+      <c r="K64" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="L64" s="175"/>
-      <c r="M64" s="175"/>
-      <c r="N64" s="175"/>
-      <c r="O64" s="175"/>
-      <c r="P64" s="175"/>
-      <c r="Q64" s="175"/>
-      <c r="R64" s="175"/>
-      <c r="S64" s="175"/>
-      <c r="T64" s="176"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+      <c r="T64" s="4"/>
     </row>
     <row r="65" customHeight="1" spans="2:20">
-      <c r="B65" s="165"/>
-      <c r="C65" s="166"/>
-      <c r="D65" s="166"/>
-      <c r="E65" s="166"/>
-      <c r="F65" s="167"/>
-      <c r="H65" s="165"/>
-      <c r="I65" s="167"/>
-      <c r="K65" s="171" t="s">
+      <c r="B65" s="33"/>
+      <c r="C65" s="91"/>
+      <c r="D65" s="91"/>
+      <c r="E65" s="91"/>
+      <c r="F65" s="34"/>
+      <c r="H65" s="33"/>
+      <c r="I65" s="34"/>
+      <c r="K65" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="L65" s="175"/>
-      <c r="M65" s="175"/>
-      <c r="N65" s="175"/>
-      <c r="O65" s="175"/>
-      <c r="P65" s="175"/>
-      <c r="Q65" s="175"/>
-      <c r="R65" s="175"/>
-      <c r="S65" s="175"/>
-      <c r="T65" s="176"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+      <c r="T65" s="4"/>
     </row>
     <row r="66" customHeight="1" spans="2:20">
-      <c r="B66" s="165"/>
-      <c r="C66" s="166"/>
-      <c r="D66" s="166"/>
-      <c r="E66" s="166"/>
-      <c r="F66" s="167"/>
-      <c r="H66" s="165"/>
-      <c r="I66" s="167"/>
-      <c r="K66" s="171" t="s">
+      <c r="B66" s="33"/>
+      <c r="C66" s="91"/>
+      <c r="D66" s="91"/>
+      <c r="E66" s="91"/>
+      <c r="F66" s="34"/>
+      <c r="H66" s="33"/>
+      <c r="I66" s="34"/>
+      <c r="K66" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="L66" s="173"/>
-      <c r="M66" s="173"/>
-      <c r="N66" s="173"/>
-      <c r="O66" s="172"/>
-      <c r="P66" s="174" t="s">
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Q66" s="173"/>
-      <c r="R66" s="173"/>
-      <c r="S66" s="173"/>
-      <c r="T66" s="172"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="4"/>
     </row>
     <row r="67" customHeight="1" spans="2:20">
-      <c r="B67" s="165"/>
-      <c r="C67" s="166"/>
-      <c r="D67" s="166"/>
-      <c r="E67" s="166"/>
-      <c r="F67" s="167"/>
-      <c r="H67" s="165"/>
-      <c r="I67" s="167"/>
-      <c r="K67" s="174" t="s">
+      <c r="B67" s="33"/>
+      <c r="C67" s="91"/>
+      <c r="D67" s="91"/>
+      <c r="E67" s="91"/>
+      <c r="F67" s="34"/>
+      <c r="H67" s="33"/>
+      <c r="I67" s="34"/>
+      <c r="K67" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="L67" s="173"/>
-      <c r="M67" s="173"/>
-      <c r="N67" s="173"/>
-      <c r="O67" s="172"/>
-      <c r="P67" s="174" t="s">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="Q67" s="173"/>
-      <c r="R67" s="173"/>
-      <c r="S67" s="173"/>
-      <c r="T67" s="172"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="4"/>
     </row>
     <row r="68" customHeight="1" spans="2:20">
-      <c r="B68" s="165"/>
-      <c r="C68" s="166"/>
-      <c r="D68" s="166"/>
-      <c r="E68" s="166"/>
-      <c r="F68" s="167"/>
-      <c r="H68" s="165"/>
-      <c r="I68" s="167"/>
-      <c r="K68" s="174" t="s">
+      <c r="B68" s="33"/>
+      <c r="C68" s="91"/>
+      <c r="D68" s="91"/>
+      <c r="E68" s="91"/>
+      <c r="F68" s="34"/>
+      <c r="H68" s="33"/>
+      <c r="I68" s="34"/>
+      <c r="K68" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="L68" s="173"/>
-      <c r="M68" s="173"/>
-      <c r="N68" s="173"/>
-      <c r="O68" s="172"/>
-      <c r="P68" s="174" t="s">
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="Q68" s="173"/>
-      <c r="R68" s="173"/>
-      <c r="S68" s="173"/>
-      <c r="T68" s="172"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="4"/>
     </row>
     <row r="69" customHeight="1" spans="2:20">
-      <c r="B69" s="165"/>
-      <c r="C69" s="166"/>
-      <c r="D69" s="166"/>
-      <c r="E69" s="166"/>
-      <c r="F69" s="167"/>
-      <c r="H69" s="165"/>
-      <c r="I69" s="167"/>
+      <c r="B69" s="33"/>
+      <c r="C69" s="91"/>
+      <c r="D69" s="91"/>
+      <c r="E69" s="91"/>
+      <c r="F69" s="34"/>
+      <c r="H69" s="33"/>
+      <c r="I69" s="34"/>
       <c r="K69" s="75" t="s">
         <v>147</v>
       </c>
-      <c r="L69" s="163"/>
-      <c r="M69" s="163"/>
-      <c r="N69" s="163"/>
-      <c r="O69" s="163"/>
-      <c r="P69" s="163"/>
-      <c r="Q69" s="163"/>
-      <c r="R69" s="163"/>
-      <c r="S69" s="163"/>
-      <c r="T69" s="164"/>
+      <c r="L69" s="55"/>
+      <c r="M69" s="55"/>
+      <c r="N69" s="55"/>
+      <c r="O69" s="55"/>
+      <c r="P69" s="55"/>
+      <c r="Q69" s="55"/>
+      <c r="R69" s="55"/>
+      <c r="S69" s="55"/>
+      <c r="T69" s="31"/>
     </row>
     <row r="70" customHeight="1" spans="2:20">
-      <c r="B70" s="168"/>
-      <c r="C70" s="170"/>
-      <c r="D70" s="170"/>
-      <c r="E70" s="170"/>
-      <c r="F70" s="169"/>
-      <c r="H70" s="168"/>
-      <c r="I70" s="169"/>
-      <c r="K70" s="168"/>
-      <c r="L70" s="170"/>
-      <c r="M70" s="170"/>
-      <c r="N70" s="170"/>
-      <c r="O70" s="170"/>
-      <c r="P70" s="170"/>
-      <c r="Q70" s="170"/>
-      <c r="R70" s="170"/>
-      <c r="S70" s="170"/>
-      <c r="T70" s="169"/>
+      <c r="B70" s="35"/>
+      <c r="C70" s="56"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="56"/>
+      <c r="F70" s="36"/>
+      <c r="H70" s="35"/>
+      <c r="I70" s="36"/>
+      <c r="K70" s="35"/>
+      <c r="L70" s="56"/>
+      <c r="M70" s="56"/>
+      <c r="N70" s="56"/>
+      <c r="O70" s="56"/>
+      <c r="P70" s="56"/>
+      <c r="Q70" s="56"/>
+      <c r="R70" s="56"/>
+      <c r="S70" s="56"/>
+      <c r="T70" s="36"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
@@ -12296,22 +12251,22 @@
       <c r="C4" s="24">
         <v>0</v>
       </c>
-      <c r="D4" s="127" t="s">
+      <c r="D4" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E4" s="127" t="s">
+      <c r="E4" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F4" s="127">
+      <c r="F4" s="107">
         <v>10</v>
       </c>
-      <c r="G4" s="127" t="s">
+      <c r="G4" s="107" t="s">
         <v>159</v>
       </c>
       <c r="H4" s="24">
         <v>18</v>
       </c>
-      <c r="I4" s="127">
+      <c r="I4" s="107">
         <v>2</v>
       </c>
       <c r="J4" s="28" t="s">
@@ -12325,22 +12280,22 @@
       <c r="C5" s="24">
         <v>50</v>
       </c>
-      <c r="D5" s="127">
+      <c r="D5" s="107">
         <v>1</v>
       </c>
-      <c r="E5" s="127" t="s">
+      <c r="E5" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F5" s="127">
+      <c r="F5" s="107">
         <v>1</v>
       </c>
-      <c r="G5" s="127" t="s">
+      <c r="G5" s="107" t="s">
         <v>158</v>
       </c>
       <c r="H5" s="24">
         <v>18</v>
       </c>
-      <c r="I5" s="127">
+      <c r="I5" s="107">
         <v>2</v>
       </c>
       <c r="J5" s="32"/>
@@ -12352,13 +12307,13 @@
       <c r="C6" s="24">
         <v>100</v>
       </c>
-      <c r="D6" s="127" t="s">
+      <c r="D6" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="127" t="s">
+      <c r="E6" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F6" s="127">
+      <c r="F6" s="107">
         <v>1</v>
       </c>
       <c r="G6" s="24" t="s">
@@ -12367,7 +12322,7 @@
       <c r="H6" s="24">
         <v>18</v>
       </c>
-      <c r="I6" s="127">
+      <c r="I6" s="107">
         <v>2</v>
       </c>
       <c r="J6" s="32"/>
@@ -12379,29 +12334,29 @@
       <c r="C7" s="24">
         <v>150</v>
       </c>
-      <c r="D7" s="127">
+      <c r="D7" s="107">
         <v>1</v>
       </c>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127">
+      <c r="E7" s="107"/>
+      <c r="F7" s="107">
         <v>1</v>
       </c>
-      <c r="G7" s="127" t="s">
+      <c r="G7" s="107" t="s">
         <v>162</v>
       </c>
       <c r="H7" s="24">
         <v>18</v>
       </c>
-      <c r="I7" s="127">
+      <c r="I7" s="107">
         <v>2</v>
       </c>
       <c r="J7" s="29"/>
     </row>
     <row r="8" ht="10" customHeight="1" spans="2:10">
-      <c r="D8" s="128"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="128"/>
-      <c r="I8" s="128"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="I8" s="108"/>
     </row>
     <row r="9" customHeight="1" spans="2:10">
       <c r="B9" s="24">
@@ -12410,13 +12365,13 @@
       <c r="C9" s="24">
         <v>300</v>
       </c>
-      <c r="D9" s="127" t="s">
+      <c r="D9" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E9" s="127">
+      <c r="E9" s="107">
         <v>1</v>
       </c>
-      <c r="F9" s="127">
+      <c r="F9" s="107">
         <v>1</v>
       </c>
       <c r="G9" s="24" t="s">
@@ -12425,7 +12380,7 @@
       <c r="H9" s="24">
         <v>19</v>
       </c>
-      <c r="I9" s="127">
+      <c r="I9" s="107">
         <v>3</v>
       </c>
       <c r="J9" s="28" t="s">
@@ -12439,13 +12394,13 @@
       <c r="C10" s="24">
         <v>500</v>
       </c>
-      <c r="D10" s="127">
+      <c r="D10" s="107">
         <v>1</v>
       </c>
-      <c r="E10" s="127" t="s">
+      <c r="E10" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="127">
+      <c r="F10" s="107">
         <v>1</v>
       </c>
       <c r="G10" s="24" t="s">
@@ -12454,7 +12409,7 @@
       <c r="H10" s="24">
         <v>19</v>
       </c>
-      <c r="I10" s="127">
+      <c r="I10" s="107">
         <v>3</v>
       </c>
       <c r="J10" s="32"/>
@@ -12466,13 +12421,13 @@
       <c r="C11" s="24">
         <v>800</v>
       </c>
-      <c r="D11" s="127" t="s">
+      <c r="D11" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E11" s="127" t="s">
+      <c r="E11" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F11" s="127">
+      <c r="F11" s="107">
         <v>1</v>
       </c>
       <c r="G11" s="24" t="s">
@@ -12481,7 +12436,7 @@
       <c r="H11" s="24">
         <v>19</v>
       </c>
-      <c r="I11" s="127">
+      <c r="I11" s="107">
         <v>3</v>
       </c>
       <c r="J11" s="32"/>
@@ -12493,13 +12448,13 @@
       <c r="C12" s="24">
         <v>1200</v>
       </c>
-      <c r="D12" s="127">
+      <c r="D12" s="107">
         <v>1</v>
       </c>
-      <c r="E12" s="127">
+      <c r="E12" s="107">
         <v>1</v>
       </c>
-      <c r="F12" s="127">
+      <c r="F12" s="107">
         <v>1</v>
       </c>
       <c r="G12" s="24" t="s">
@@ -12508,16 +12463,16 @@
       <c r="H12" s="24">
         <v>19</v>
       </c>
-      <c r="I12" s="127">
+      <c r="I12" s="107">
         <v>3</v>
       </c>
       <c r="J12" s="29"/>
     </row>
     <row r="13" ht="10" customHeight="1" spans="2:10">
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
-      <c r="I13" s="128"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="I13" s="108"/>
     </row>
     <row r="14" customHeight="1" spans="2:10">
       <c r="B14" s="24">
@@ -12526,13 +12481,13 @@
       <c r="C14" s="24">
         <v>1600</v>
       </c>
-      <c r="D14" s="127" t="s">
+      <c r="D14" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E14" s="127" t="s">
+      <c r="E14" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F14" s="127">
+      <c r="F14" s="107">
         <v>1</v>
       </c>
       <c r="G14" s="24" t="s">
@@ -12541,7 +12496,7 @@
       <c r="H14" s="24">
         <v>20</v>
       </c>
-      <c r="I14" s="127">
+      <c r="I14" s="107">
         <v>4</v>
       </c>
       <c r="J14" s="28" t="s">
@@ -12555,22 +12510,22 @@
       <c r="C15" s="24">
         <v>2000</v>
       </c>
-      <c r="D15" s="127">
+      <c r="D15" s="107">
         <v>1</v>
       </c>
-      <c r="E15" s="127" t="s">
+      <c r="E15" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F15" s="127">
+      <c r="F15" s="107">
         <v>1</v>
       </c>
-      <c r="G15" s="127" t="s">
+      <c r="G15" s="107" t="s">
         <v>158</v>
       </c>
       <c r="H15" s="24">
         <v>20</v>
       </c>
-      <c r="I15" s="127">
+      <c r="I15" s="107">
         <v>4</v>
       </c>
       <c r="J15" s="32"/>
@@ -12582,13 +12537,13 @@
       <c r="C16" s="24">
         <v>2400</v>
       </c>
-      <c r="D16" s="127" t="s">
+      <c r="D16" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="107">
         <v>1</v>
       </c>
-      <c r="F16" s="127">
+      <c r="F16" s="107">
         <v>1</v>
       </c>
       <c r="G16" s="24" t="s">
@@ -12597,7 +12552,7 @@
       <c r="H16" s="24">
         <v>20</v>
       </c>
-      <c r="I16" s="127">
+      <c r="I16" s="107">
         <v>4</v>
       </c>
       <c r="J16" s="32"/>
@@ -12609,13 +12564,13 @@
       <c r="C17" s="24">
         <v>2800</v>
       </c>
-      <c r="D17" s="127">
+      <c r="D17" s="107">
         <v>1</v>
       </c>
-      <c r="E17" s="127" t="s">
+      <c r="E17" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F17" s="127">
+      <c r="F17" s="107">
         <v>1</v>
       </c>
       <c r="G17" s="24" t="s">
@@ -12624,16 +12579,16 @@
       <c r="H17" s="24">
         <v>20</v>
       </c>
-      <c r="I17" s="127">
+      <c r="I17" s="107">
         <v>4</v>
       </c>
       <c r="J17" s="29"/>
     </row>
     <row r="18" ht="10" customHeight="1" spans="2:10">
-      <c r="D18" s="128"/>
-      <c r="E18" s="128"/>
-      <c r="F18" s="128"/>
-      <c r="I18" s="128"/>
+      <c r="D18" s="108"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="108"/>
+      <c r="I18" s="108"/>
     </row>
     <row r="19" customHeight="1" spans="2:10">
       <c r="B19" s="24">
@@ -12642,13 +12597,13 @@
       <c r="C19" s="24">
         <v>3200</v>
       </c>
-      <c r="D19" s="127" t="s">
+      <c r="D19" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E19" s="127" t="s">
+      <c r="E19" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F19" s="127">
+      <c r="F19" s="107">
         <v>1</v>
       </c>
       <c r="G19" s="24" t="s">
@@ -12657,7 +12612,7 @@
       <c r="H19" s="24">
         <v>21</v>
       </c>
-      <c r="I19" s="127">
+      <c r="I19" s="107">
         <v>5</v>
       </c>
       <c r="J19" s="28" t="s">
@@ -12671,22 +12626,22 @@
       <c r="C20" s="24">
         <v>3600</v>
       </c>
-      <c r="D20" s="127">
+      <c r="D20" s="107">
         <v>1</v>
       </c>
-      <c r="E20" s="127">
+      <c r="E20" s="107">
         <v>1</v>
       </c>
-      <c r="F20" s="127">
+      <c r="F20" s="107">
         <v>1</v>
       </c>
-      <c r="G20" s="127" t="s">
+      <c r="G20" s="107" t="s">
         <v>158</v>
       </c>
       <c r="H20" s="24">
         <v>21</v>
       </c>
-      <c r="I20" s="127">
+      <c r="I20" s="107">
         <v>5</v>
       </c>
       <c r="J20" s="32"/>
@@ -12698,13 +12653,13 @@
       <c r="C21" s="24">
         <v>4000</v>
       </c>
-      <c r="D21" s="127" t="s">
+      <c r="D21" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E21" s="127" t="s">
+      <c r="E21" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F21" s="127">
+      <c r="F21" s="107">
         <v>1</v>
       </c>
       <c r="G21" s="24" t="s">
@@ -12713,7 +12668,7 @@
       <c r="H21" s="24">
         <v>21</v>
       </c>
-      <c r="I21" s="127">
+      <c r="I21" s="107">
         <v>5</v>
       </c>
       <c r="J21" s="32"/>
@@ -12725,13 +12680,13 @@
       <c r="C22" s="24">
         <v>5000</v>
       </c>
-      <c r="D22" s="127">
+      <c r="D22" s="107">
         <v>1</v>
       </c>
-      <c r="E22" s="127" t="s">
+      <c r="E22" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F22" s="127">
+      <c r="F22" s="107">
         <v>1</v>
       </c>
       <c r="G22" s="24" t="s">
@@ -12740,16 +12695,16 @@
       <c r="H22" s="24">
         <v>21</v>
       </c>
-      <c r="I22" s="127">
+      <c r="I22" s="107">
         <v>5</v>
       </c>
       <c r="J22" s="29"/>
     </row>
     <row r="23" ht="10" customHeight="1" spans="2:10">
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="I23" s="128"/>
+      <c r="D23" s="108"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
+      <c r="I23" s="108"/>
     </row>
     <row r="24" customHeight="1" spans="2:10">
       <c r="B24" s="24">
@@ -12758,22 +12713,22 @@
       <c r="C24" s="24">
         <v>10000</v>
       </c>
-      <c r="D24" s="127" t="s">
+      <c r="D24" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E24" s="127">
+      <c r="E24" s="107">
         <v>1</v>
       </c>
-      <c r="F24" s="127">
+      <c r="F24" s="107">
         <v>1</v>
       </c>
-      <c r="G24" s="127" t="s">
+      <c r="G24" s="107" t="s">
         <v>158</v>
       </c>
       <c r="H24" s="24">
         <v>22</v>
       </c>
-      <c r="I24" s="127">
+      <c r="I24" s="107">
         <v>6</v>
       </c>
       <c r="J24" s="28" t="s">
@@ -12787,13 +12742,13 @@
       <c r="C25" s="24">
         <v>15000</v>
       </c>
-      <c r="D25" s="127">
+      <c r="D25" s="107">
         <v>1</v>
       </c>
-      <c r="E25" s="127" t="s">
+      <c r="E25" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F25" s="127">
+      <c r="F25" s="107">
         <v>1</v>
       </c>
       <c r="G25" s="24" t="s">
@@ -12802,7 +12757,7 @@
       <c r="H25" s="24">
         <v>23</v>
       </c>
-      <c r="I25" s="127">
+      <c r="I25" s="107">
         <v>6</v>
       </c>
       <c r="J25" s="32"/>
@@ -12814,13 +12769,13 @@
       <c r="C26" s="24">
         <v>20000</v>
       </c>
-      <c r="D26" s="127" t="s">
+      <c r="D26" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E26" s="127" t="s">
+      <c r="E26" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F26" s="127">
+      <c r="F26" s="107">
         <v>1</v>
       </c>
       <c r="G26" s="24" t="s">
@@ -12829,16 +12784,16 @@
       <c r="H26" s="24">
         <v>24</v>
       </c>
-      <c r="I26" s="127">
+      <c r="I26" s="107">
         <v>6</v>
       </c>
       <c r="J26" s="29"/>
     </row>
     <row r="27" ht="10" customHeight="1" spans="2:10">
-      <c r="D27" s="128"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="128"/>
-      <c r="I27" s="128"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
+      <c r="I27" s="108"/>
     </row>
     <row r="28" customHeight="1" spans="2:10">
       <c r="B28" s="24">
@@ -12847,13 +12802,13 @@
       <c r="C28" s="24">
         <v>30000</v>
       </c>
-      <c r="D28" s="127">
+      <c r="D28" s="107">
         <v>1</v>
       </c>
-      <c r="E28" s="127">
+      <c r="E28" s="107">
         <v>1</v>
       </c>
-      <c r="F28" s="127">
+      <c r="F28" s="107">
         <v>2</v>
       </c>
       <c r="G28" s="24" t="s">
@@ -12862,7 +12817,7 @@
       <c r="H28" s="24">
         <v>25</v>
       </c>
-      <c r="I28" s="127">
+      <c r="I28" s="107">
         <v>8</v>
       </c>
       <c r="J28" s="24" t="s">
@@ -12878,10 +12833,10 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="129" t="s">
+      <c r="I30" s="109" t="s">
         <v>179</v>
       </c>
-      <c r="J30" s="130"/>
+      <c r="J30" s="110"/>
     </row>
     <row r="31" customHeight="1" spans="2:10">
       <c r="B31" s="2" t="s">
@@ -12892,10 +12847,10 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="4"/>
-      <c r="I31" s="131" t="s">
+      <c r="I31" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="J31" s="132"/>
+      <c r="J31" s="112"/>
     </row>
     <row r="32" customHeight="1" spans="2:10">
       <c r="B32" s="24" t="s">
@@ -12916,8 +12871,8 @@
       <c r="G32" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="I32" s="133"/>
-      <c r="J32" s="134"/>
+      <c r="I32" s="113"/>
+      <c r="J32" s="114"/>
     </row>
     <row r="33" customHeight="1" spans="2:10">
       <c r="B33" s="24">
@@ -12926,20 +12881,20 @@
       <c r="C33" s="24">
         <v>0</v>
       </c>
-      <c r="D33" s="127" t="s">
+      <c r="D33" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E33" s="127" t="s">
+      <c r="E33" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F33" s="127">
+      <c r="F33" s="107">
         <v>4</v>
       </c>
-      <c r="G33" s="127" t="s">
+      <c r="G33" s="107" t="s">
         <v>182</v>
       </c>
-      <c r="I33" s="133"/>
-      <c r="J33" s="134"/>
+      <c r="I33" s="113"/>
+      <c r="J33" s="114"/>
     </row>
     <row r="34" customHeight="1" spans="2:10">
       <c r="B34" s="24">
@@ -12948,20 +12903,20 @@
       <c r="C34" s="24">
         <v>100</v>
       </c>
-      <c r="D34" s="127">
+      <c r="D34" s="107">
         <v>1</v>
       </c>
-      <c r="E34" s="127" t="s">
+      <c r="E34" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F34" s="127">
+      <c r="F34" s="107">
         <v>1</v>
       </c>
-      <c r="G34" s="127" t="s">
+      <c r="G34" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="I34" s="133"/>
-      <c r="J34" s="134"/>
+      <c r="I34" s="113"/>
+      <c r="J34" s="114"/>
     </row>
     <row r="35" customHeight="1" spans="2:10">
       <c r="B35" s="24">
@@ -12970,20 +12925,20 @@
       <c r="C35" s="24">
         <v>200</v>
       </c>
-      <c r="D35" s="127" t="s">
+      <c r="D35" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E35" s="127" t="s">
+      <c r="E35" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F35" s="127">
+      <c r="F35" s="107">
         <v>1</v>
       </c>
-      <c r="G35" s="127" t="s">
+      <c r="G35" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="I35" s="133"/>
-      <c r="J35" s="134"/>
+      <c r="I35" s="113"/>
+      <c r="J35" s="114"/>
     </row>
     <row r="36" customHeight="1" spans="2:10">
       <c r="B36" s="24">
@@ -12992,18 +12947,18 @@
       <c r="C36" s="24">
         <v>300</v>
       </c>
-      <c r="D36" s="127">
+      <c r="D36" s="107">
         <v>1</v>
       </c>
-      <c r="E36" s="127"/>
-      <c r="F36" s="127">
+      <c r="E36" s="107"/>
+      <c r="F36" s="107">
         <v>1</v>
       </c>
-      <c r="G36" s="127" t="s">
+      <c r="G36" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="I36" s="133"/>
-      <c r="J36" s="134"/>
+      <c r="I36" s="113"/>
+      <c r="J36" s="114"/>
     </row>
     <row r="37" customHeight="1" spans="2:10">
       <c r="B37" s="24">
@@ -13012,20 +12967,20 @@
       <c r="C37" s="24">
         <v>600</v>
       </c>
-      <c r="D37" s="127" t="s">
+      <c r="D37" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E37" s="127">
+      <c r="E37" s="107">
         <v>1</v>
       </c>
-      <c r="F37" s="127">
+      <c r="F37" s="107">
         <v>1</v>
       </c>
-      <c r="G37" s="127" t="s">
+      <c r="G37" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="I37" s="133"/>
-      <c r="J37" s="134"/>
+      <c r="I37" s="113"/>
+      <c r="J37" s="114"/>
     </row>
     <row r="38" customHeight="1" spans="2:10">
       <c r="B38" s="24">
@@ -13034,20 +12989,20 @@
       <c r="C38" s="24">
         <v>1000</v>
       </c>
-      <c r="D38" s="127">
+      <c r="D38" s="107">
         <v>1</v>
       </c>
-      <c r="E38" s="127" t="s">
+      <c r="E38" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F38" s="127">
+      <c r="F38" s="107">
         <v>1</v>
       </c>
-      <c r="G38" s="127" t="s">
+      <c r="G38" s="107" t="s">
         <v>184</v>
       </c>
-      <c r="I38" s="133"/>
-      <c r="J38" s="134"/>
+      <c r="I38" s="113"/>
+      <c r="J38" s="114"/>
     </row>
     <row r="39" customHeight="1" spans="2:10">
       <c r="B39" s="24">
@@ -13056,20 +13011,20 @@
       <c r="C39" s="24">
         <v>1600</v>
       </c>
-      <c r="D39" s="127" t="s">
+      <c r="D39" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E39" s="127" t="s">
+      <c r="E39" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F39" s="127">
+      <c r="F39" s="107">
         <v>1</v>
       </c>
-      <c r="G39" s="127" t="s">
+      <c r="G39" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="I39" s="133"/>
-      <c r="J39" s="134"/>
+      <c r="I39" s="113"/>
+      <c r="J39" s="114"/>
     </row>
     <row r="40" customHeight="1" spans="2:10">
       <c r="B40" s="24">
@@ -13078,20 +13033,20 @@
       <c r="C40" s="24">
         <v>2400</v>
       </c>
-      <c r="D40" s="127">
+      <c r="D40" s="107">
         <v>1</v>
       </c>
-      <c r="E40" s="127">
+      <c r="E40" s="107">
         <v>1</v>
       </c>
-      <c r="F40" s="127">
+      <c r="F40" s="107">
         <v>1</v>
       </c>
-      <c r="G40" s="127" t="s">
+      <c r="G40" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="I40" s="133"/>
-      <c r="J40" s="134"/>
+      <c r="I40" s="113"/>
+      <c r="J40" s="114"/>
     </row>
     <row r="41" customHeight="1" spans="2:10">
       <c r="B41" s="24">
@@ -13100,20 +13055,20 @@
       <c r="C41" s="24">
         <v>3200</v>
       </c>
-      <c r="D41" s="127" t="s">
+      <c r="D41" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E41" s="127" t="s">
+      <c r="E41" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F41" s="127">
+      <c r="F41" s="107">
         <v>1</v>
       </c>
-      <c r="G41" s="127" t="s">
+      <c r="G41" s="107" t="s">
         <v>185</v>
       </c>
-      <c r="I41" s="133"/>
-      <c r="J41" s="134"/>
+      <c r="I41" s="113"/>
+      <c r="J41" s="114"/>
     </row>
     <row r="42" customHeight="1" spans="2:10">
       <c r="B42" s="24">
@@ -13122,20 +13077,20 @@
       <c r="C42" s="24">
         <v>4000</v>
       </c>
-      <c r="D42" s="127">
+      <c r="D42" s="107">
         <v>1</v>
       </c>
-      <c r="E42" s="127" t="s">
+      <c r="E42" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="127">
+      <c r="F42" s="107">
         <v>1</v>
       </c>
-      <c r="G42" s="127" t="s">
+      <c r="G42" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="I42" s="133"/>
-      <c r="J42" s="134"/>
+      <c r="I42" s="113"/>
+      <c r="J42" s="114"/>
     </row>
     <row r="43" customHeight="1" spans="2:10">
       <c r="B43" s="24">
@@ -13144,20 +13099,20 @@
       <c r="C43" s="24">
         <v>4800</v>
       </c>
-      <c r="D43" s="127" t="s">
+      <c r="D43" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E43" s="127">
+      <c r="E43" s="107">
         <v>1</v>
       </c>
-      <c r="F43" s="127">
+      <c r="F43" s="107">
         <v>1</v>
       </c>
-      <c r="G43" s="127" t="s">
+      <c r="G43" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="I43" s="133"/>
-      <c r="J43" s="134"/>
+      <c r="I43" s="113"/>
+      <c r="J43" s="114"/>
     </row>
     <row r="44" customHeight="1" spans="2:10">
       <c r="B44" s="24">
@@ -13166,20 +13121,20 @@
       <c r="C44" s="24">
         <v>5600</v>
       </c>
-      <c r="D44" s="127">
+      <c r="D44" s="107">
         <v>1</v>
       </c>
-      <c r="E44" s="127" t="s">
+      <c r="E44" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F44" s="127">
+      <c r="F44" s="107">
         <v>1</v>
       </c>
-      <c r="G44" s="127" t="s">
+      <c r="G44" s="107" t="s">
         <v>186</v>
       </c>
-      <c r="I44" s="133"/>
-      <c r="J44" s="134"/>
+      <c r="I44" s="113"/>
+      <c r="J44" s="114"/>
     </row>
     <row r="45" customHeight="1" spans="2:10">
       <c r="B45" s="24">
@@ -13188,20 +13143,20 @@
       <c r="C45" s="24">
         <v>6400</v>
       </c>
-      <c r="D45" s="127" t="s">
+      <c r="D45" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E45" s="127" t="s">
+      <c r="E45" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F45" s="127">
+      <c r="F45" s="107">
         <v>1</v>
       </c>
-      <c r="G45" s="127" t="s">
+      <c r="G45" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="I45" s="133"/>
-      <c r="J45" s="134"/>
+      <c r="I45" s="113"/>
+      <c r="J45" s="114"/>
     </row>
     <row r="46" customHeight="1" spans="2:10">
       <c r="B46" s="24">
@@ -13210,20 +13165,20 @@
       <c r="C46" s="24">
         <v>7200</v>
       </c>
-      <c r="D46" s="127">
+      <c r="D46" s="107">
         <v>1</v>
       </c>
-      <c r="E46" s="127">
+      <c r="E46" s="107">
         <v>1</v>
       </c>
-      <c r="F46" s="127">
+      <c r="F46" s="107">
         <v>1</v>
       </c>
-      <c r="G46" s="127" t="s">
+      <c r="G46" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="I46" s="133"/>
-      <c r="J46" s="134"/>
+      <c r="I46" s="113"/>
+      <c r="J46" s="114"/>
     </row>
     <row r="47" customHeight="1" spans="2:10">
       <c r="B47" s="24">
@@ -13232,20 +13187,20 @@
       <c r="C47" s="24">
         <v>8000</v>
       </c>
-      <c r="D47" s="127" t="s">
+      <c r="D47" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="E47" s="127" t="s">
+      <c r="E47" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="F47" s="127">
+      <c r="F47" s="107">
         <v>1</v>
       </c>
-      <c r="G47" s="127" t="s">
+      <c r="G47" s="107" t="s">
         <v>187</v>
       </c>
-      <c r="I47" s="135"/>
-      <c r="J47" s="136"/>
+      <c r="I47" s="115"/>
+      <c r="J47" s="116"/>
     </row>
     <row r="49" customHeight="1" spans="2:10">
       <c r="B49" s="2" t="s">
@@ -14012,7 +13967,7 @@
       <c r="D12" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="126" t="s">
+      <c r="E12" s="106" t="s">
         <v>241</v>
       </c>
       <c r="F12" s="24" t="s">
@@ -14706,12 +14661,12 @@
       <c r="C8" s="82"/>
       <c r="D8" s="82"/>
       <c r="E8" s="82"/>
-      <c r="F8" s="83"/>
+      <c r="F8" s="72"/>
       <c r="H8" s="81"/>
       <c r="I8" s="82"/>
       <c r="J8" s="82"/>
       <c r="K8" s="82"/>
-      <c r="L8" s="83"/>
+      <c r="L8" s="72"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="10" customHeight="1" spans="2:19">
       <c r="H9" s="74"/>
@@ -14728,56 +14683,56 @@
       <c r="S9" s="74"/>
     </row>
     <row r="10" s="74" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="71" t="s">
         <v>266</v>
       </c>
-      <c r="C10" s="85" t="s">
+      <c r="C10" s="83" t="s">
         <v>267</v>
       </c>
-      <c r="D10" s="86" t="s">
+      <c r="D10" s="84" t="s">
         <v>268</v>
       </c>
-      <c r="E10" s="87" t="s">
+      <c r="E10" s="85" t="s">
         <v>269</v>
       </c>
-      <c r="F10" s="88" t="s">
+      <c r="F10" s="86" t="s">
         <v>270</v>
       </c>
-      <c r="H10" s="84" t="s">
+      <c r="H10" s="71" t="s">
         <v>271</v>
       </c>
-      <c r="I10" s="84">
+      <c r="I10" s="71">
         <v>3</v>
       </c>
-      <c r="J10" s="89" t="s">
+      <c r="J10" s="75" t="s">
         <v>272</v>
       </c>
-      <c r="K10" s="90"/>
-      <c r="L10" s="91"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="31"/>
     </row>
     <row r="11" s="74" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B11" s="92"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="95"/>
-      <c r="F11" s="96"/>
-      <c r="H11" s="92"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="99"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="90"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="91"/>
+      <c r="L11" s="34"/>
     </row>
     <row r="12" s="74" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B12" s="100"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="104"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="107"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="95"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="36"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="10" customHeight="1" spans="2:19">
       <c r="H13" s="74"/>
@@ -14794,50 +14749,50 @@
       <c r="S13" s="74"/>
     </row>
     <row r="14" s="74" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B14" s="85" t="s">
+      <c r="B14" s="83" t="s">
         <v>267</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C14" s="75" t="s">
         <v>273</v>
       </c>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="91"/>
-      <c r="H14" s="84" t="s">
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="31"/>
+      <c r="H14" s="71" t="s">
         <v>271</v>
       </c>
-      <c r="I14" s="108" t="s">
+      <c r="I14" s="96" t="s">
         <v>274</v>
       </c>
-      <c r="J14" s="89" t="s">
+      <c r="J14" s="75" t="s">
         <v>275</v>
       </c>
-      <c r="K14" s="90"/>
-      <c r="L14" s="91"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="31"/>
     </row>
     <row r="15" s="74" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B15" s="93"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="99"/>
-      <c r="H15" s="92"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="99"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="34"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="34"/>
     </row>
     <row r="16" s="74" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B16" s="101"/>
-      <c r="C16" s="105"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="107"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="105"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="107"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="36"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="36"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="10" customHeight="1" spans="2:19">
       <c r="H17" s="74"/>
@@ -14854,50 +14809,50 @@
       <c r="S17" s="74"/>
     </row>
     <row r="18" s="74" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="84" t="s">
         <v>268</v>
       </c>
-      <c r="C18" s="89" t="s">
+      <c r="C18" s="75" t="s">
         <v>276</v>
       </c>
-      <c r="D18" s="90"/>
-      <c r="E18" s="90"/>
-      <c r="F18" s="91"/>
-      <c r="H18" s="84" t="s">
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="31"/>
+      <c r="H18" s="71" t="s">
         <v>271</v>
       </c>
-      <c r="I18" s="108" t="s">
+      <c r="I18" s="96" t="s">
         <v>277</v>
       </c>
-      <c r="J18" s="89" t="s">
+      <c r="J18" s="75" t="s">
         <v>278</v>
       </c>
-      <c r="K18" s="90"/>
-      <c r="L18" s="91"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" s="74" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B19" s="94"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="99"/>
-      <c r="H19" s="92"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="99"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="34"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="91"/>
+      <c r="L19" s="34"/>
     </row>
     <row r="20" s="74" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B20" s="102"/>
-      <c r="C20" s="105"/>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="107"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="107"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="36"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="36"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="10" customHeight="1" spans="2:19">
       <c r="H21" s="74"/>
@@ -14914,22 +14869,22 @@
       <c r="S21" s="74"/>
     </row>
     <row r="22" customHeight="1" spans="2:19">
-      <c r="B22" s="87" t="s">
+      <c r="B22" s="85" t="s">
         <v>269</v>
       </c>
-      <c r="C22" s="89" t="s">
+      <c r="C22" s="75" t="s">
         <v>279</v>
       </c>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="91"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="31"/>
     </row>
     <row r="23" customHeight="1" spans="2:19">
-      <c r="B23" s="95"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="99"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="34"/>
       <c r="H23" s="2" t="s">
         <v>280</v>
       </c>
@@ -14939,25 +14894,25 @@
       <c r="L23" s="4"/>
     </row>
     <row r="24" customHeight="1" spans="2:19">
-      <c r="B24" s="103"/>
-      <c r="C24" s="105"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="107"/>
-      <c r="H24" s="109" t="s">
+      <c r="B24" s="94"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="36"/>
+      <c r="H24" s="97" t="s">
         <v>281</v>
       </c>
-      <c r="I24" s="110"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="110"/>
-      <c r="L24" s="111"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="98"/>
+      <c r="K24" s="98"/>
+      <c r="L24" s="99"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="10" customHeight="1" spans="2:19">
-      <c r="H25" s="112"/>
-      <c r="I25" s="113"/>
-      <c r="J25" s="113"/>
-      <c r="K25" s="113"/>
-      <c r="L25" s="114"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="101"/>
+      <c r="J25" s="101"/>
+      <c r="K25" s="101"/>
+      <c r="L25" s="102"/>
       <c r="M25" s="74"/>
       <c r="N25" s="74"/>
       <c r="O25" s="74"/>
@@ -14967,51 +14922,51 @@
       <c r="S25" s="74"/>
     </row>
     <row r="26" customHeight="1" spans="2:19">
-      <c r="B26" s="88" t="s">
+      <c r="B26" s="86" t="s">
         <v>270</v>
       </c>
-      <c r="C26" s="89" t="s">
+      <c r="C26" s="75" t="s">
         <v>282</v>
       </c>
-      <c r="D26" s="115"/>
-      <c r="E26" s="115"/>
-      <c r="F26" s="116"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="113"/>
-      <c r="J26" s="113"/>
-      <c r="K26" s="113"/>
-      <c r="L26" s="114"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="77"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="101"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="101"/>
+      <c r="L26" s="102"/>
     </row>
     <row r="27" customHeight="1" spans="2:19">
-      <c r="B27" s="96"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="119"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="113"/>
-      <c r="J27" s="113"/>
-      <c r="K27" s="113"/>
-      <c r="L27" s="114"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="80"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="102"/>
     </row>
     <row r="28" customHeight="1" spans="2:19">
-      <c r="B28" s="104"/>
-      <c r="C28" s="120"/>
-      <c r="D28" s="121"/>
-      <c r="E28" s="121"/>
-      <c r="F28" s="122"/>
-      <c r="H28" s="112"/>
-      <c r="I28" s="113"/>
-      <c r="J28" s="113"/>
-      <c r="K28" s="113"/>
-      <c r="L28" s="114"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="72"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="101"/>
+      <c r="L28" s="102"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="10" customHeight="1" spans="2:19">
-      <c r="H29" s="112"/>
-      <c r="I29" s="113"/>
-      <c r="J29" s="113"/>
-      <c r="K29" s="113"/>
-      <c r="L29" s="114"/>
+      <c r="H29" s="100"/>
+      <c r="I29" s="101"/>
+      <c r="J29" s="101"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="102"/>
       <c r="M29" s="74"/>
       <c r="N29" s="74"/>
       <c r="O29" s="74"/>
@@ -15028,11 +14983,11 @@
       <c r="D30" s="76"/>
       <c r="E30" s="76"/>
       <c r="F30" s="77"/>
-      <c r="H30" s="112"/>
-      <c r="I30" s="113"/>
-      <c r="J30" s="113"/>
-      <c r="K30" s="113"/>
-      <c r="L30" s="114"/>
+      <c r="H30" s="100"/>
+      <c r="I30" s="101"/>
+      <c r="J30" s="101"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="102"/>
     </row>
     <row r="31" customHeight="1" spans="2:19">
       <c r="B31" s="78"/>
@@ -15040,11 +14995,11 @@
       <c r="D31" s="79"/>
       <c r="E31" s="79"/>
       <c r="F31" s="80"/>
-      <c r="H31" s="112"/>
-      <c r="I31" s="113"/>
-      <c r="J31" s="113"/>
-      <c r="K31" s="113"/>
-      <c r="L31" s="114"/>
+      <c r="H31" s="100"/>
+      <c r="I31" s="101"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="101"/>
+      <c r="L31" s="102"/>
     </row>
     <row r="32" customHeight="1" spans="2:19">
       <c r="B32" s="78"/>
@@ -15052,23 +15007,23 @@
       <c r="D32" s="79"/>
       <c r="E32" s="79"/>
       <c r="F32" s="80"/>
-      <c r="H32" s="112"/>
-      <c r="I32" s="113"/>
-      <c r="J32" s="113"/>
-      <c r="K32" s="113"/>
-      <c r="L32" s="114"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="102"/>
     </row>
     <row r="33" customHeight="1" spans="2:12">
       <c r="B33" s="81"/>
       <c r="C33" s="82"/>
       <c r="D33" s="82"/>
       <c r="E33" s="82"/>
-      <c r="F33" s="83"/>
-      <c r="H33" s="123"/>
-      <c r="I33" s="124"/>
-      <c r="J33" s="124"/>
-      <c r="K33" s="124"/>
-      <c r="L33" s="125"/>
+      <c r="F33" s="72"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="29">

--- a/冒险者基础规则.xlsx
+++ b/冒险者基础规则.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\斯诺德\游玩过程开启面板\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\斯诺德\游玩过程开启面板\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="基本规则" sheetId="6" r:id="rId1"/>
@@ -2593,13 +2593,9 @@
 同样会减半。</t>
   </si>
   <si>
-    <t>角色在使用双持武器造成伤害时，仅需要投掷一次武器伤
-害骰，在造成伤害时额额外附加一半的结算后伤害值（例
-如敏捷属性调整值为3的游荡者使用两把匕首武器攻击，那
-么伤害公式为（1D4+3）+（1D4+3）÷2。
-如果角色的双持武器不同名，那么附加伤害仅计算伤害骰
-较低的那把武器（例如同时持有传奇武器和普通单手剑，
-在附加伤害时取用普通单手剑的伤害公式）。
+    <t>角色在使用两把相同类型的双持武器造成伤害时，仅需要
+投掷一次武器伤害骰，在造成伤害时额外结算一次对应武
+器给予的属性调整值加成值，并且攻击命中检定值+1。
 需要双手装备的武器（例如双手剑、斧、长枪、弓箭或猎
 枪等）在每个自身回合中拥有一次重掷攻击命中检定骰的
 机会，持有者必须接受这次重掷的结果，如果在此之前角
@@ -3987,7 +3983,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4506,15 +4502,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -5308,11 +5295,11 @@
       <c r="R29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="2:18">
-      <c r="B30" s="173"/>
-      <c r="C30" s="174"/>
-      <c r="D30" s="174"/>
-      <c r="E30" s="174"/>
-      <c r="F30" s="175"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="10"/>
       <c r="H30" s="8"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
@@ -5439,21 +5426,21 @@
       <c r="R37" s="7"/>
     </row>
     <row r="38" customHeight="1" spans="2:18">
-      <c r="B38" s="173"/>
-      <c r="C38" s="174"/>
-      <c r="D38" s="174"/>
-      <c r="E38" s="174"/>
-      <c r="F38" s="175"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="10"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
       <c r="L38" s="10"/>
-      <c r="N38" s="173"/>
-      <c r="O38" s="174"/>
-      <c r="P38" s="174"/>
-      <c r="Q38" s="174"/>
-      <c r="R38" s="175"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="10"/>
     </row>
     <row r="39" customHeight="1" spans="2:18">
       <c r="B39" s="8"/>
